--- a/output/forecast_PJ-2021-E_align-on_行程グループ.xlsx
+++ b/output/forecast_PJ-2021-E_align-on_行程グループ.xlsx
@@ -150,9 +150,9 @@
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1560,7 +1560,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'段階予測'!L131</f>
+              <f>'段階予測'!M133</f>
             </strRef>
           </tx>
           <spPr>
@@ -1570,12 +1570,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'段階予測'!$B$132:$B$136</f>
+              <f>'段階予測'!$B$134:$B$138</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$L$132:$L$136</f>
+              <f>'段階予測'!$M$134:$M$138</f>
             </numRef>
           </val>
         </ser>
@@ -3038,9 +3038,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>17</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3240000"/>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 12:49</t>
+          <t>2026-09-03 21:06</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:P195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8928,16 +8928,17 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9421,7 +9422,7 @@
         <v>16709</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>13293.2</v>
+        <v>12803.6</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>18133.4</v>
@@ -9446,7 +9447,7 @@
         <v>18710.1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>13548.9</v>
+        <v>13049.8</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>15271.7</v>
@@ -9471,7 +9472,7 @@
         <v>20556.3</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>13952.3</v>
+        <v>13438.5</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>16417.5</v>
@@ -9496,7 +9497,7 @@
         <v>21120.6</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>14180.1</v>
+        <v>13657.8</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>14656</v>
@@ -9521,7 +9522,7 @@
         <v>20770.2</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>13767.5</v>
+        <v>13260.5</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>13886.2</v>
@@ -9546,7 +9547,7 @@
         <v>21253.3</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>14028.4</v>
+        <v>13511.7</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>13614.7</v>
@@ -9571,7 +9572,7 @@
         <v>20494.6</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>14059.4</v>
+        <v>13541.6</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>14580.3</v>
@@ -9596,7 +9597,7 @@
         <v>21365.4</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>14938.2</v>
+        <v>14388</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>15865.3</v>
@@ -9621,7 +9622,7 @@
         <v>21719.8</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>14844.5</v>
+        <v>14297.7</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>18226.2</v>
@@ -9646,7 +9647,7 @@
         <v>18708.8</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>12495.2</v>
+        <v>12035</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>17827.1</v>
@@ -9671,7 +9672,7 @@
         <v>20129.4</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>15897.1</v>
+        <v>15311.6</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>22013.8</v>
@@ -9696,10 +9697,10 @@
         <v>16722.2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>15446</v>
+        <v>14877.1</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>12050.9</v>
+        <v>9608.700000000001</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>17769.7</v>
@@ -9721,10 +9722,10 @@
         <v>16140.2</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>15013.7</v>
+        <v>14460.8</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>11814.3</v>
+        <v>9420.1</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>15747.8</v>
@@ -9746,10 +9747,10 @@
         <v>14874.5</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>13897.5</v>
+        <v>13385.6</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>11039.8</v>
+        <v>8802.6</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>11049.5</v>
@@ -9771,10 +9772,10 @@
         <v>13998.6</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>13127.8</v>
+        <v>12644.3</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>10548.5</v>
+        <v>8410.799999999999</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>10147.8</v>
@@ -9796,10 +9797,10 @@
         <v>12179.1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>11504.7</v>
+        <v>11081</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>9375.6</v>
+        <v>7475.6</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>8637.799999999999</v>
@@ -9821,13 +9822,13 @@
         <v>10119.6</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>9646.9</v>
+        <v>9291.5</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>8037.5</v>
+        <v>6408.7</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>9970.799999999999</v>
+        <v>604.2</v>
       </c>
     </row>
     <row r="40">
@@ -9846,13 +9847,13 @@
         <v>10233.8</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>9815.5</v>
+        <v>9454</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>8448.5</v>
+        <v>6736.3</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>7760.9</v>
+        <v>470.3</v>
       </c>
     </row>
     <row r="41">
@@ -9871,13 +9872,13 @@
         <v>6891.6</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>6689.1</v>
+        <v>6442.7</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>5933.8</v>
+        <v>4731.3</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>5585.1</v>
+        <v>338.4</v>
       </c>
     </row>
     <row r="42">
@@ -9896,13 +9897,13 @@
         <v>4910.3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>4808.2</v>
+        <v>4631.1</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>4361.3</v>
+        <v>3477.5</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>5052.2</v>
+        <v>306.1</v>
       </c>
     </row>
     <row r="66">
@@ -11053,519 +11054,588 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
+          <t>「見込んだ総工数」は どの段階でも同じ値になる。総工数は契約人月(または見積もり)で決まっており、実績を確定させても動かないため。確定分が既にそれを超えている段階だけ、実績そのものが下限になって大きくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>「残工数の倍率」は 残工数 ÷ 学習カーブが残り区間に置く量。1.0 なら学習カーブどおり。1 より大きいほど確定分が学習カーブより少なく、そのずれが残り区間へ上乗せされる。切り替え点の段差の高さは この倍率そのもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
           <t>終盤の段階ほど残り区間は短く、量も小さい。誤差率はその小さい分母で割った値なので数字が跳ねやすい。「残りが全体に占める割合」を見て、どれだけの量に対する誤差なのかと併せて読むこと。</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>区切り</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>確定した月</t>
         </is>
       </c>
-      <c r="D131" s="8" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>確定月数</t>
         </is>
       </c>
-      <c r="E131" s="8" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>見込んだ総工数(時間)</t>
         </is>
       </c>
-      <c r="F131" s="8" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>残工数の倍率(学習カーブ比)</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>残り月数</t>
         </is>
       </c>
-      <c r="G131" s="8" t="inlineStr">
+      <c r="H133" s="8" t="inlineStr">
         <is>
           <t>評価した月数</t>
         </is>
       </c>
-      <c r="H131" s="8" t="inlineStr">
+      <c r="I133" s="8" t="inlineStr">
         <is>
           <t>残り実績(時間)</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="J133" s="8" t="inlineStr">
         <is>
           <t>残りが全体に占める割合(%)</t>
         </is>
       </c>
-      <c r="J131" s="8" t="inlineStr">
+      <c r="K133" s="8" t="inlineStr">
         <is>
           <t>残り予測(時間)</t>
         </is>
       </c>
-      <c r="K131" s="8" t="inlineStr">
+      <c r="L133" s="8" t="inlineStr">
         <is>
           <t>残り総量誤差(%)</t>
         </is>
       </c>
-      <c r="L131" s="8" t="inlineStr">
+      <c r="M133" s="8" t="inlineStr">
         <is>
           <t>残り月次WAPE</t>
         </is>
       </c>
-      <c r="M131" s="8" t="inlineStr">
+      <c r="N133" s="8" t="inlineStr">
         <is>
           <t>残りピーク月ズレ</t>
         </is>
       </c>
-      <c r="N131" s="8" t="inlineStr">
+      <c r="O133" s="8" t="inlineStr">
         <is>
           <t>累積カーブ最大乖離</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="P133" s="8" t="inlineStr">
         <is>
           <t>総量誤差(%)</t>
         </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t>(なし)</t>
-        </is>
-      </c>
-      <c r="C132" s="10" t="inlineStr">
-        <is>
-          <t>(なし)</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>472000</v>
-      </c>
-      <c r="F132" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="G132" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>482150.4</v>
-      </c>
-      <c r="I132" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="J132" s="12" t="n">
-        <v>472000</v>
-      </c>
-      <c r="K132" s="23" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="L132" s="22" t="n">
-        <v>0.3642</v>
-      </c>
-      <c r="M132" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N132" s="22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="O132" s="23" t="n">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E133" s="12" t="n">
-        <v>472000</v>
-      </c>
-      <c r="F133" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="G133" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>420709.6</v>
-      </c>
-      <c r="I133" s="23" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="J133" s="12" t="n">
-        <v>410559.2</v>
-      </c>
-      <c r="K133" s="23" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="L133" s="22" t="n">
-        <v>0.3866</v>
-      </c>
-      <c r="M133" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N133" s="22" t="n">
-        <v>0.1659</v>
-      </c>
-      <c r="O133" s="23" t="n">
-        <v>-2.1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>α版</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>481390.4</v>
-      </c>
-      <c r="F134" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G134" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="H134" s="12" t="n">
-        <v>255714.2</v>
-      </c>
-      <c r="I134" s="23" t="n">
-        <v>53</v>
-      </c>
-      <c r="J134" s="12" t="n">
-        <v>254954.2</v>
-      </c>
-      <c r="K134" s="23" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="L134" s="22" t="n">
-        <v>0.2235</v>
-      </c>
-      <c r="M134" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" s="22" t="n">
-        <v>0.0579</v>
-      </c>
-      <c r="O134" s="23" t="n">
-        <v>-0.2</v>
+        <v>472000</v>
+      </c>
+      <c r="F134" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H134" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="I134" s="12" t="n">
+        <v>482150.4</v>
+      </c>
+      <c r="J134" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="K134" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="L134" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M134" s="22" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="N134" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O134" s="22" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P134" s="24" t="n">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>β版</t>
+          <t>プロトタイプ</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>488538.7</v>
-      </c>
-      <c r="F135" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="G135" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="H135" s="12" t="n">
-        <v>75222</v>
-      </c>
-      <c r="I135" s="23" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J135" s="12" t="n">
-        <v>81610.3</v>
-      </c>
-      <c r="K135" s="23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L135" s="22" t="n">
-        <v>0.3418</v>
-      </c>
-      <c r="M135" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="22" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="O135" s="23" t="n">
-        <v>1.3</v>
+        <v>472000</v>
+      </c>
+      <c r="F135" s="23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H135" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="I135" s="12" t="n">
+        <v>420709.6</v>
+      </c>
+      <c r="J135" s="24" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>410559.2</v>
+      </c>
+      <c r="L135" s="24" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M135" s="22" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="N135" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O135" s="22" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="P135" s="24" t="n">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>α版</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E136" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="F136" s="23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H136" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="I136" s="12" t="n">
+        <v>255714.2</v>
+      </c>
+      <c r="J136" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="K136" s="12" t="n">
+        <v>245563.8</v>
+      </c>
+      <c r="L136" s="24" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="N136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="22" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="P136" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>β版</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="F137" s="23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H137" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I137" s="12" t="n">
+        <v>75222</v>
+      </c>
+      <c r="J137" s="24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K137" s="12" t="n">
+        <v>65071.6</v>
+      </c>
+      <c r="L137" s="24" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="M137" s="22" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="N137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="22" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="P137" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>マスターアップ</t>
         </is>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="D136" s="10" t="n">
+      <c r="D138" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="E136" s="12" t="n">
-        <v>498649.9</v>
-      </c>
-      <c r="F136" s="10" t="n">
+      <c r="E138" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="F138" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G138" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G136" s="11" t="n">
+      <c r="H138" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H136" s="12" t="n">
+      <c r="I138" s="12" t="n">
         <v>11869.4</v>
       </c>
-      <c r="I136" s="23" t="n">
+      <c r="J138" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="J136" s="12" t="n">
-        <v>28368.9</v>
-      </c>
-      <c r="K136" s="23" t="n">
-        <v>139</v>
-      </c>
-      <c r="L136" s="22" t="n">
-        <v>1.3901</v>
-      </c>
-      <c r="M136" s="10" t="n">
+      <c r="K138" s="12" t="n">
+        <v>1719</v>
+      </c>
+      <c r="L138" s="24" t="n">
+        <v>-85.5</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>0.8552</v>
+      </c>
+      <c r="N138" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N136" s="22" t="n">
-        <v>0.0323</v>
-      </c>
-      <c r="O136" s="23" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
+      <c r="O138" s="22" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="P138" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
         <is>
           <t>■ 各段階の条件</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="24" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="25" t="inlineStr">
         <is>
           <t>段階0 着手前</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・実績を一切使わない全期間予測。マイルストーンの日付も使っていない(着手前に通過済みのマイルストーンは無いため)。「予測」シートは記入済みの日付をすべて使うので、その分だけ条件が違う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・実績を一切使わない全期間予測。マイルストーンの日付も使っていない(着手前に通過済みのマイルストーンは無いため)。「予測」シートは記入済みの日付をすべて使うので、その分だけ条件が違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・マイルストーンの指定が無いため、学習カーブをそのまま期間に貼っています。</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="24" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="25" t="inlineStr">
         <is>
           <t>段階1 プロトタイプ後(2021-10まで確定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2021-01〜2021-10 の 10 ヶ月を実績で確定し、残り 26 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+          <t xml:space="preserve">  ・2021-01〜2021-10 の 10 ヶ月を実績で確定し、残り 26 ヶ月を予測している。</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・マイルストーンの指定が無いため、学習カーブをそのまま期間に貼っています。</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="24" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="25" t="inlineStr">
         <is>
           <t>段階2 α版後(2022-04まで確定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2021-01〜2022-04 の 16 ヶ月を実績で確定し、残り 20 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+          <t xml:space="preserve">  ・2021-01〜2022-04 の 16 ヶ月を実績で確定し、残り 20 ヶ月を予測している。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="24" t="inlineStr">
-        <is>
-          <t>段階3 β版後(2023-03まで確定)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・2021-01〜2023-03 の 27 ヶ月を実績で確定し、残り 9 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
+          <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: 企画・プリプロ(計 9,390 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+      <c r="A179" s="25" t="inlineStr">
+        <is>
+          <t>段階3 β版後(2023-03まで確定)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版</t>
+          <t xml:space="preserve">  ・2021-01〜2023-03 の 27 ヶ月を実績で確定し、残り 9 ヶ月を予測している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="24" t="inlineStr">
-        <is>
-          <t>段階4 マスターアップ後(2023-08まで確定)</t>
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・2021-01〜2023-08 の 32 ヶ月を実績で確定し、残り 4 ヶ月を予測している。</t>
+          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ, マスターアップ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
+          <t xml:space="preserve">  ・確定分の実績が学習カーブの見込みより多いため、残り区間に配る工数が学習カーブの 0.65 倍になっている。総工数は動かさない決まりなので、そのずれは残り区間へ寄せるほかなく、2023-03 の直後に下へ段差が出る。この案件は学習した消化ペースから外れている、と読むこと。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版, マスターアップ</t>
+          <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: ゲームデザイン・シナリオ, 企画・プリプロ(計 16,539 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="25" t="inlineStr">
+        <is>
+          <t>段階4 マスターアップ後(2023-08まで確定)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・2021-01〜2023-08 の 32 ヶ月を実績で確定し、残り 4 ヶ月を予測している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ, マスターアップ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版, マスターアップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・確定分の実績が学習カーブの見込みより多いため、残り区間に配る工数が学習カーブの 0.10 倍になっている。総工数は動かさない決まりなので、そのずれは残り区間へ寄せるほかなく、2023-08 の直後に下へ段差が出る。この案件は学習した消化ペースから外れている、と読むこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: アート, ゲームデザイン・シナリオ, サウンド, 企画・プリプロ(計 26,650 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
         <is>
           <t>※ PJ-2021-E は完了案件として学習データに入っているため、段階予測では自分自身を学習から外した 9 件で学習し直している(自分の実績で学習したカーブで自分を予測すると評価にならない)。</t>
         </is>
@@ -23147,7 +23217,7 @@
       <c r="F7" s="22" t="n">
         <v>0.1309</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="24" t="n">
         <v>3.3</v>
       </c>
       <c r="H7" s="13" t="n">
@@ -23175,7 +23245,7 @@
       <c r="F8" s="22" t="n">
         <v>0.1362</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="24" t="n">
         <v>3.7</v>
       </c>
       <c r="H8" s="13" t="n">
@@ -23203,7 +23273,7 @@
       <c r="F9" s="22" t="n">
         <v>0.1151</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="24" t="n">
         <v>1.4</v>
       </c>
       <c r="H9" s="13" t="n">
@@ -23231,7 +23301,7 @@
       <c r="F10" s="22" t="n">
         <v>0.1311</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="24" t="n">
         <v>3.4</v>
       </c>
       <c r="H10" s="13" t="n">
@@ -23259,7 +23329,7 @@
       <c r="F11" s="22" t="n">
         <v>0.1366</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="24" t="n">
         <v>4.2</v>
       </c>
       <c r="H11" s="13" t="n">
@@ -23287,7 +23357,7 @@
       <c r="F12" s="22" t="n">
         <v>0.1151</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="24" t="n">
         <v>1.4</v>
       </c>
       <c r="H12" s="13" t="n">
@@ -77478,7 +77548,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>2026-09-03 12:49:05</t>
+          <t>2026-09-03 21:06:20</t>
         </is>
       </c>
     </row>
@@ -77818,7 +77888,7 @@
           <t>新規タイトル開発</t>
         </is>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="12" t="n">
@@ -77853,7 +77923,7 @@
           <t>大型アップデート</t>
         </is>
       </c>
-      <c r="D36" s="25" t="n">
+      <c r="D36" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="12" t="n">
@@ -77888,7 +77958,7 @@
           <t>新規タイトル開発</t>
         </is>
       </c>
-      <c r="D37" s="25" t="n">
+      <c r="D37" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="12" t="n">
@@ -77923,7 +77993,7 @@
           <t>移植・リマスター</t>
         </is>
       </c>
-      <c r="D38" s="25" t="n">
+      <c r="D38" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="12" t="n">
@@ -77958,7 +78028,7 @@
           <t>新規タイトル開発</t>
         </is>
       </c>
-      <c r="D39" s="25" t="n">
+      <c r="D39" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="12" t="n">
@@ -77993,7 +78063,7 @@
           <t>大型アップデート</t>
         </is>
       </c>
-      <c r="D40" s="25" t="n">
+      <c r="D40" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="12" t="n">
@@ -78028,7 +78098,7 @@
           <t>新規タイトル開発</t>
         </is>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="12" t="n">
@@ -78063,7 +78133,7 @@
           <t>大型アップデート</t>
         </is>
       </c>
-      <c r="D42" s="25" t="n">
+      <c r="D42" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="12" t="n">
@@ -78098,7 +78168,7 @@
           <t>移植・リマスター</t>
         </is>
       </c>
-      <c r="D43" s="25" t="n">
+      <c r="D43" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="12" t="n">
@@ -78133,7 +78203,7 @@
           <t>新規タイトル開発</t>
         </is>
       </c>
-      <c r="D44" s="25" t="n">
+      <c r="D44" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="12" t="n">

--- a/output/forecast_PJ-2021-E_align-on_行程グループ.xlsx
+++ b/output/forecast_PJ-2021-E_align-on_行程グループ.xlsx
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:06</t>
+          <t>2026-09-03 22:20</t>
         </is>
       </c>
     </row>
@@ -77548,7 +77548,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:06:20</t>
+          <t>2026-09-03 22:20:38</t>
         </is>
       </c>
     </row>

--- a/output/forecast_PJ-2021-E_align-on_行程グループ.xlsx
+++ b/output/forecast_PJ-2021-E_align-on_行程グループ.xlsx
@@ -985,7 +985,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'段階予測'!B6</f>
+              <f>'段階予測'!B7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1006,12 +1006,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$7:$A$42</f>
+              <f>'段階予測'!$A$8:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$B$7:$B$42</f>
+              <f>'段階予測'!$B$8:$B$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1021,7 +1021,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'段階予測'!C6</f>
+              <f>'段階予測'!C7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1039,12 +1039,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$7:$A$42</f>
+              <f>'段階予測'!$A$8:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$C$7:$C$42</f>
+              <f>'段階予測'!$C$8:$C$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1054,7 +1054,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'段階予測'!D6</f>
+              <f>'段階予測'!D7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1072,12 +1072,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$7:$A$42</f>
+              <f>'段階予測'!$A$8:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$D$7:$D$42</f>
+              <f>'段階予測'!$D$8:$D$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1087,7 +1087,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'段階予測'!E6</f>
+              <f>'段階予測'!E7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1105,12 +1105,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$7:$A$42</f>
+              <f>'段階予測'!$A$8:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$E$7:$E$42</f>
+              <f>'段階予測'!$E$8:$E$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1120,7 +1120,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'段階予測'!F6</f>
+              <f>'段階予測'!F7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1138,12 +1138,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$7:$A$42</f>
+              <f>'段階予測'!$A$8:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$F$7:$F$42</f>
+              <f>'段階予測'!$F$8:$F$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1153,7 +1153,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'段階予測'!G6</f>
+              <f>'段階予測'!G7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1171,12 +1171,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$7:$A$42</f>
+              <f>'段階予測'!$A$8:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$G$7:$G$42</f>
+              <f>'段階予測'!$G$8:$G$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1272,7 +1272,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'段階予測'!B68</f>
+              <f>'段階予測'!B69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1293,12 +1293,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$69:$A$104</f>
+              <f>'段階予測'!$A$70:$A$105</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$B$69:$B$104</f>
+              <f>'段階予測'!$B$70:$B$105</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1308,7 +1308,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'段階予測'!C68</f>
+              <f>'段階予測'!C69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1326,12 +1326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$69:$A$104</f>
+              <f>'段階予測'!$A$70:$A$105</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$C$69:$C$104</f>
+              <f>'段階予測'!$C$70:$C$105</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1341,7 +1341,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'段階予測'!D68</f>
+              <f>'段階予測'!D69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1359,12 +1359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$69:$A$104</f>
+              <f>'段階予測'!$A$70:$A$105</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$D$69:$D$104</f>
+              <f>'段階予測'!$D$70:$D$105</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1374,7 +1374,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'段階予測'!E68</f>
+              <f>'段階予測'!E69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1392,12 +1392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$69:$A$104</f>
+              <f>'段階予測'!$A$70:$A$105</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$E$69:$E$104</f>
+              <f>'段階予測'!$E$70:$E$105</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1407,7 +1407,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'段階予測'!F68</f>
+              <f>'段階予測'!F69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1425,12 +1425,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$69:$A$104</f>
+              <f>'段階予測'!$A$70:$A$105</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$F$69:$F$104</f>
+              <f>'段階予測'!$F$70:$F$105</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1440,7 +1440,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'段階予測'!G68</f>
+              <f>'段階予測'!G69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1458,12 +1458,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'段階予測'!$A$69:$A$104</f>
+              <f>'段階予測'!$A$70:$A$105</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$G$69:$G$104</f>
+              <f>'段階予測'!$G$70:$G$105</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1560,7 +1560,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'段階予測'!M133</f>
+              <f>'段階予測'!N135</f>
             </strRef>
           </tx>
           <spPr>
@@ -1570,12 +1570,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'段階予測'!$B$134:$B$138</f>
+              <f>'段階予測'!$B$136:$B$140</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'段階予測'!$M$134:$M$138</f>
+              <f>'段階予測'!$N$136:$N$140</f>
             </numRef>
           </val>
         </ser>
@@ -2996,7 +2996,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10728000" cy="4320000"/>
@@ -3018,7 +3018,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10728000" cy="4320000"/>
@@ -3038,9 +3038,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>132</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3240000"/>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:20</t>
+          <t>2026-09-04 00:45</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P195"/>
+  <dimension ref="A1:Q197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8929,16 +8929,17 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8962,1029 +8963,1006 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>立ち上がり上限: 前月比 1.33 倍/月(実績の前月比の分布から決めた値)。人員は急には増やせないため、確定区間の直後に工数が跳ねないよう増加率に上限を置き、あふれた工数を後ろの月へ送っている。総工数と行程グループ別の総量は動かしていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>■ 月次工数(時間)  実績 と 各段階の予測</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>段階0 着手前</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>段階1 プロトタイプ後(2021-10まで確定)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>段階2 α版後(2022-04まで確定)</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>段階3 β版後(2023-03まで確定)</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>段階4 マスターアップ後(2023-08まで確定)</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>2212.8</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>5346.2</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>2212.8</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>2212.8</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>2212.8</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>2212.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>3289.4</v>
+        <v>2212.8</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>5485.4</v>
+        <v>5346.2</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>3289.4</v>
+        <v>2212.8</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3289.4</v>
+        <v>2212.8</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>3289.4</v>
+        <v>2212.8</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>3289.4</v>
+        <v>2212.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>4610.7</v>
+        <v>3289.4</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>7230.1</v>
+        <v>5485.4</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>4610.7</v>
+        <v>3289.4</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>4610.7</v>
+        <v>3289.4</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4610.7</v>
+        <v>3289.4</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>4610.7</v>
+        <v>3289.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>5392.8</v>
+        <v>4610.7</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>7352.1</v>
+        <v>7230.1</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>5392.8</v>
+        <v>4610.7</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>5392.8</v>
+        <v>4610.7</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>5392.8</v>
+        <v>4610.7</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>5392.8</v>
+        <v>4610.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>5875.1</v>
+        <v>5392.8</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>8397.5</v>
+        <v>7352.1</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>5875.1</v>
+        <v>5392.8</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>5875.1</v>
+        <v>5392.8</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>5875.1</v>
+        <v>5392.8</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>5875.1</v>
+        <v>5392.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>6664.2</v>
+        <v>5875.1</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>8613.5</v>
+        <v>8397.5</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>6664.2</v>
+        <v>5875.1</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>6664.2</v>
+        <v>5875.1</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>6664.2</v>
+        <v>5875.1</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>6664.2</v>
+        <v>5875.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>7114.2</v>
+        <v>6664.2</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>9062.799999999999</v>
+        <v>8613.5</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>7114.2</v>
+        <v>6664.2</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>7114.2</v>
+        <v>6664.2</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>7114.2</v>
+        <v>6664.2</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>7114.2</v>
+        <v>6664.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>7159.8</v>
+        <v>7114.2</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>9486.1</v>
+        <v>9062.799999999999</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>7159.8</v>
+        <v>7114.2</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>7159.8</v>
+        <v>7114.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>7159.8</v>
+        <v>7114.2</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>7159.8</v>
+        <v>7114.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>7725.3</v>
+        <v>7159.8</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>9967.799999999999</v>
+        <v>9486.1</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>7725.3</v>
+        <v>7159.8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>7725.3</v>
+        <v>7159.8</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>7725.3</v>
+        <v>7159.8</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>7725.3</v>
+        <v>7159.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>11396.5</v>
+        <v>7725.3</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>11157.5</v>
+        <v>9967.799999999999</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>11396.5</v>
+        <v>7725.3</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>11396.5</v>
+        <v>7725.3</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>11396.5</v>
+        <v>7725.3</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>11396.5</v>
+        <v>7725.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>22707.4</v>
+        <v>11396.5</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>11255.7</v>
+        <v>11157.5</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>11298.4</v>
+        <v>11396.5</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>22707.4</v>
+        <v>11396.5</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>22707.4</v>
+        <v>11396.5</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>22707.4</v>
+        <v>11396.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>24332.8</v>
+        <v>22707.4</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>13081.6</v>
+        <v>11255.7</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>13387.7</v>
+        <v>11298.4</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>24332.8</v>
+        <v>22707.4</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>24332.8</v>
+        <v>22707.4</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>24332.8</v>
+        <v>22707.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>28940.1</v>
+        <v>24332.8</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>13331.2</v>
+        <v>13081.6</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>13730.5</v>
+        <v>13387.7</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>28940.1</v>
+        <v>24332.8</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>28940.1</v>
+        <v>24332.8</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>28940.1</v>
+        <v>24332.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>28533.6</v>
+        <v>28940.1</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>12773.9</v>
+        <v>13331.2</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>13319.6</v>
+        <v>13730.5</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>28533.6</v>
+        <v>28940.1</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>28533.6</v>
+        <v>28940.1</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>28533.6</v>
+        <v>28940.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>39513.1</v>
+        <v>28533.6</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>14675.1</v>
+        <v>12773.9</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>15339.3</v>
+        <v>13319.6</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>39513.1</v>
+        <v>28533.6</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>39513.1</v>
+        <v>28533.6</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>39513.1</v>
+        <v>28533.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>20968.4</v>
+        <v>39513.1</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>15044.3</v>
+        <v>14675.1</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>15876.3</v>
+        <v>15339.3</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>20968.4</v>
+        <v>39513.1</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>20968.4</v>
+        <v>39513.1</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>20968.4</v>
+        <v>39513.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>18133.4</v>
+        <v>20968.4</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>15798.6</v>
+        <v>15044.3</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>16709</v>
+        <v>15876.3</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>12803.6</v>
+        <v>20968.4</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>18133.4</v>
+        <v>20968.4</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>18133.4</v>
+        <v>20968.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>15271.7</v>
+        <v>18133.4</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>17608.1</v>
+        <v>15798.6</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>18710.1</v>
+        <v>16709</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>13049.8</v>
+        <v>12803.6</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>15271.7</v>
+        <v>18133.4</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>15271.7</v>
+        <v>18133.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>16417.5</v>
+        <v>15271.7</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>19288.4</v>
+        <v>17608.1</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>20556.3</v>
+        <v>18710.1</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>13438.5</v>
+        <v>13049.8</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>16417.5</v>
+        <v>15271.7</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>16417.5</v>
+        <v>15271.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>14656</v>
+        <v>16417.5</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>19789</v>
+        <v>19288.4</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>21120.6</v>
+        <v>20556.3</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>13657.8</v>
+        <v>13438.5</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>14656</v>
+        <v>16417.5</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>14656</v>
+        <v>16417.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>13886.2</v>
+        <v>14656</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>19461.6</v>
+        <v>19789</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>20770.2</v>
+        <v>21120.6</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>13260.5</v>
+        <v>13657.8</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>13886.2</v>
+        <v>14656</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>13886.2</v>
+        <v>14656</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>13614.7</v>
+        <v>13886.2</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>19919.5</v>
+        <v>19461.6</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>21253.3</v>
+        <v>20770.2</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>13511.7</v>
+        <v>13260.5</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>13614.7</v>
+        <v>13886.2</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>13614.7</v>
+        <v>13886.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>14580.3</v>
+        <v>13614.7</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>19232</v>
+        <v>19919.5</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>20494.6</v>
+        <v>21253.3</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>13541.6</v>
+        <v>13511.7</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>14580.3</v>
+        <v>13614.7</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>14580.3</v>
+        <v>13614.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>15865.3</v>
+        <v>14580.3</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>20099.6</v>
+        <v>19232</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>21365.4</v>
+        <v>20494.6</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>14388</v>
+        <v>13541.6</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>15865.3</v>
+        <v>14580.3</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>15865.3</v>
+        <v>14580.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>18226.2</v>
+        <v>15865.3</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>20481.4</v>
+        <v>20099.6</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>21719.8</v>
+        <v>21365.4</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>14297.7</v>
+        <v>14388</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>18226.2</v>
+        <v>15865.3</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>18226.2</v>
+        <v>15865.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>17827.1</v>
+        <v>18226.2</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>17680.7</v>
+        <v>20481.4</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>18708.8</v>
+        <v>21719.8</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>12035</v>
+        <v>14297.7</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>17827.1</v>
+        <v>18226.2</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>17827.1</v>
+        <v>18226.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>22013.8</v>
+        <v>17827.1</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>19050.8</v>
+        <v>17680.7</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>20129.4</v>
+        <v>18708.8</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>15311.6</v>
+        <v>12035</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>22013.8</v>
+        <v>17827.1</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>22013.8</v>
+        <v>17827.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>17769.7</v>
+        <v>22013.8</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>15833.8</v>
+        <v>19050.8</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>16722.2</v>
+        <v>20129.4</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>14877.1</v>
+        <v>15311.6</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>9608.700000000001</v>
+        <v>22013.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>17769.7</v>
+        <v>22013.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>15747.8</v>
+        <v>17769.7</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>15320.2</v>
+        <v>15833.8</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>16140.2</v>
+        <v>16722.2</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>14460.8</v>
+        <v>14877.1</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>9420.1</v>
+        <v>9608.700000000001</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>15747.8</v>
+        <v>17769.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>11049.5</v>
+        <v>15747.8</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>14144.4</v>
+        <v>15320.2</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>14874.5</v>
+        <v>16140.2</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>13385.6</v>
+        <v>14460.8</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>8802.6</v>
+        <v>9420.1</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>11049.5</v>
+        <v>15747.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>10147.8</v>
+        <v>11049.5</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>13330.9</v>
+        <v>14144.4</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>13998.6</v>
+        <v>14874.5</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>12644.3</v>
+        <v>13385.6</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>8410.799999999999</v>
+        <v>8802.6</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>10147.8</v>
+        <v>11049.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>8637.799999999999</v>
+        <v>10147.8</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>11642.5</v>
+        <v>13330.9</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>12179.1</v>
+        <v>13998.6</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>11081</v>
+        <v>12644.3</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>7475.6</v>
+        <v>8410.799999999999</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>8637.799999999999</v>
+        <v>10147.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>5590.1</v>
+        <v>8637.799999999999</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>9722.200000000001</v>
+        <v>11642.5</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>10119.6</v>
+        <v>12179.1</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>9291.5</v>
+        <v>11081</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6408.7</v>
+        <v>7475.6</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>604.2</v>
+        <v>8637.799999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>3746.3</v>
+        <v>5590.1</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>9866.9</v>
+        <v>9722.200000000001</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>10233.8</v>
+        <v>10119.6</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>9454</v>
+        <v>9291.5</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>6736.3</v>
+        <v>6408.7</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>470.3</v>
+        <v>604.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>1912.1</v>
+        <v>3746.3</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>6684.6</v>
+        <v>9866.9</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>6891.6</v>
+        <v>10233.8</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>6442.7</v>
+        <v>9454</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>4731.3</v>
+        <v>6736.3</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>338.4</v>
+        <v>470.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>1912.1</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>6684.6</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>6891.6</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>6442.7</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>4731.3</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>338.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B43" s="12" t="n">
         <v>620.9</v>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C43" s="12" t="n">
         <v>4784.1</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D43" s="12" t="n">
         <v>4910.3</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>4631.1</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>3477.5</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>306.1</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>■ 累積工数(時間)  実績 と 各段階の予測</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>月次は上下に振れるため、当たり外れは累積で見るほうが分かりやすい。終点の高さの差がそのまま総量の読み違いになる。</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>段階0 着手前</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>段階1 プロトタイプ後(2021-10まで確定)</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>段階2 α版後(2022-04まで確定)</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>段階3 β版後(2023-03まで確定)</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>段階4 マスターアップ後(2023-08まで確定)</t>
         </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10">
-        <f>A7</f>
-        <v/>
-      </c>
-      <c r="B69" s="12">
-        <f>SUM(B$7:B7)</f>
-        <v/>
-      </c>
-      <c r="C69" s="12">
-        <f>SUM(C$7:C7)</f>
-        <v/>
-      </c>
-      <c r="D69" s="12">
-        <f>SUM(D$7:D7)</f>
-        <v/>
-      </c>
-      <c r="E69" s="12">
-        <f>SUM(E$7:E7)</f>
-        <v/>
-      </c>
-      <c r="F69" s="12">
-        <f>SUM(F$7:F7)</f>
-        <v/>
-      </c>
-      <c r="G69" s="12">
-        <f>SUM(G$7:G7)</f>
-        <v/>
       </c>
     </row>
     <row r="70">
@@ -9993,27 +9971,27 @@
         <v/>
       </c>
       <c r="B70" s="12">
-        <f>SUM(B$7:B8)</f>
+        <f>SUM(B$8:B8)</f>
         <v/>
       </c>
       <c r="C70" s="12">
-        <f>SUM(C$7:C8)</f>
+        <f>SUM(C$8:C8)</f>
         <v/>
       </c>
       <c r="D70" s="12">
-        <f>SUM(D$7:D8)</f>
+        <f>SUM(D$8:D8)</f>
         <v/>
       </c>
       <c r="E70" s="12">
-        <f>SUM(E$7:E8)</f>
+        <f>SUM(E$8:E8)</f>
         <v/>
       </c>
       <c r="F70" s="12">
-        <f>SUM(F$7:F8)</f>
+        <f>SUM(F$8:F8)</f>
         <v/>
       </c>
       <c r="G70" s="12">
-        <f>SUM(G$7:G8)</f>
+        <f>SUM(G$8:G8)</f>
         <v/>
       </c>
     </row>
@@ -10023,27 +10001,27 @@
         <v/>
       </c>
       <c r="B71" s="12">
-        <f>SUM(B$7:B9)</f>
+        <f>SUM(B$8:B9)</f>
         <v/>
       </c>
       <c r="C71" s="12">
-        <f>SUM(C$7:C9)</f>
+        <f>SUM(C$8:C9)</f>
         <v/>
       </c>
       <c r="D71" s="12">
-        <f>SUM(D$7:D9)</f>
+        <f>SUM(D$8:D9)</f>
         <v/>
       </c>
       <c r="E71" s="12">
-        <f>SUM(E$7:E9)</f>
+        <f>SUM(E$8:E9)</f>
         <v/>
       </c>
       <c r="F71" s="12">
-        <f>SUM(F$7:F9)</f>
+        <f>SUM(F$8:F9)</f>
         <v/>
       </c>
       <c r="G71" s="12">
-        <f>SUM(G$7:G9)</f>
+        <f>SUM(G$8:G9)</f>
         <v/>
       </c>
     </row>
@@ -10053,27 +10031,27 @@
         <v/>
       </c>
       <c r="B72" s="12">
-        <f>SUM(B$7:B10)</f>
+        <f>SUM(B$8:B10)</f>
         <v/>
       </c>
       <c r="C72" s="12">
-        <f>SUM(C$7:C10)</f>
+        <f>SUM(C$8:C10)</f>
         <v/>
       </c>
       <c r="D72" s="12">
-        <f>SUM(D$7:D10)</f>
+        <f>SUM(D$8:D10)</f>
         <v/>
       </c>
       <c r="E72" s="12">
-        <f>SUM(E$7:E10)</f>
+        <f>SUM(E$8:E10)</f>
         <v/>
       </c>
       <c r="F72" s="12">
-        <f>SUM(F$7:F10)</f>
+        <f>SUM(F$8:F10)</f>
         <v/>
       </c>
       <c r="G72" s="12">
-        <f>SUM(G$7:G10)</f>
+        <f>SUM(G$8:G10)</f>
         <v/>
       </c>
     </row>
@@ -10083,27 +10061,27 @@
         <v/>
       </c>
       <c r="B73" s="12">
-        <f>SUM(B$7:B11)</f>
+        <f>SUM(B$8:B11)</f>
         <v/>
       </c>
       <c r="C73" s="12">
-        <f>SUM(C$7:C11)</f>
+        <f>SUM(C$8:C11)</f>
         <v/>
       </c>
       <c r="D73" s="12">
-        <f>SUM(D$7:D11)</f>
+        <f>SUM(D$8:D11)</f>
         <v/>
       </c>
       <c r="E73" s="12">
-        <f>SUM(E$7:E11)</f>
+        <f>SUM(E$8:E11)</f>
         <v/>
       </c>
       <c r="F73" s="12">
-        <f>SUM(F$7:F11)</f>
+        <f>SUM(F$8:F11)</f>
         <v/>
       </c>
       <c r="G73" s="12">
-        <f>SUM(G$7:G11)</f>
+        <f>SUM(G$8:G11)</f>
         <v/>
       </c>
     </row>
@@ -10113,27 +10091,27 @@
         <v/>
       </c>
       <c r="B74" s="12">
-        <f>SUM(B$7:B12)</f>
+        <f>SUM(B$8:B12)</f>
         <v/>
       </c>
       <c r="C74" s="12">
-        <f>SUM(C$7:C12)</f>
+        <f>SUM(C$8:C12)</f>
         <v/>
       </c>
       <c r="D74" s="12">
-        <f>SUM(D$7:D12)</f>
+        <f>SUM(D$8:D12)</f>
         <v/>
       </c>
       <c r="E74" s="12">
-        <f>SUM(E$7:E12)</f>
+        <f>SUM(E$8:E12)</f>
         <v/>
       </c>
       <c r="F74" s="12">
-        <f>SUM(F$7:F12)</f>
+        <f>SUM(F$8:F12)</f>
         <v/>
       </c>
       <c r="G74" s="12">
-        <f>SUM(G$7:G12)</f>
+        <f>SUM(G$8:G12)</f>
         <v/>
       </c>
     </row>
@@ -10143,27 +10121,27 @@
         <v/>
       </c>
       <c r="B75" s="12">
-        <f>SUM(B$7:B13)</f>
+        <f>SUM(B$8:B13)</f>
         <v/>
       </c>
       <c r="C75" s="12">
-        <f>SUM(C$7:C13)</f>
+        <f>SUM(C$8:C13)</f>
         <v/>
       </c>
       <c r="D75" s="12">
-        <f>SUM(D$7:D13)</f>
+        <f>SUM(D$8:D13)</f>
         <v/>
       </c>
       <c r="E75" s="12">
-        <f>SUM(E$7:E13)</f>
+        <f>SUM(E$8:E13)</f>
         <v/>
       </c>
       <c r="F75" s="12">
-        <f>SUM(F$7:F13)</f>
+        <f>SUM(F$8:F13)</f>
         <v/>
       </c>
       <c r="G75" s="12">
-        <f>SUM(G$7:G13)</f>
+        <f>SUM(G$8:G13)</f>
         <v/>
       </c>
     </row>
@@ -10173,27 +10151,27 @@
         <v/>
       </c>
       <c r="B76" s="12">
-        <f>SUM(B$7:B14)</f>
+        <f>SUM(B$8:B14)</f>
         <v/>
       </c>
       <c r="C76" s="12">
-        <f>SUM(C$7:C14)</f>
+        <f>SUM(C$8:C14)</f>
         <v/>
       </c>
       <c r="D76" s="12">
-        <f>SUM(D$7:D14)</f>
+        <f>SUM(D$8:D14)</f>
         <v/>
       </c>
       <c r="E76" s="12">
-        <f>SUM(E$7:E14)</f>
+        <f>SUM(E$8:E14)</f>
         <v/>
       </c>
       <c r="F76" s="12">
-        <f>SUM(F$7:F14)</f>
+        <f>SUM(F$8:F14)</f>
         <v/>
       </c>
       <c r="G76" s="12">
-        <f>SUM(G$7:G14)</f>
+        <f>SUM(G$8:G14)</f>
         <v/>
       </c>
     </row>
@@ -10203,27 +10181,27 @@
         <v/>
       </c>
       <c r="B77" s="12">
-        <f>SUM(B$7:B15)</f>
+        <f>SUM(B$8:B15)</f>
         <v/>
       </c>
       <c r="C77" s="12">
-        <f>SUM(C$7:C15)</f>
+        <f>SUM(C$8:C15)</f>
         <v/>
       </c>
       <c r="D77" s="12">
-        <f>SUM(D$7:D15)</f>
+        <f>SUM(D$8:D15)</f>
         <v/>
       </c>
       <c r="E77" s="12">
-        <f>SUM(E$7:E15)</f>
+        <f>SUM(E$8:E15)</f>
         <v/>
       </c>
       <c r="F77" s="12">
-        <f>SUM(F$7:F15)</f>
+        <f>SUM(F$8:F15)</f>
         <v/>
       </c>
       <c r="G77" s="12">
-        <f>SUM(G$7:G15)</f>
+        <f>SUM(G$8:G15)</f>
         <v/>
       </c>
     </row>
@@ -10233,27 +10211,27 @@
         <v/>
       </c>
       <c r="B78" s="12">
-        <f>SUM(B$7:B16)</f>
+        <f>SUM(B$8:B16)</f>
         <v/>
       </c>
       <c r="C78" s="12">
-        <f>SUM(C$7:C16)</f>
+        <f>SUM(C$8:C16)</f>
         <v/>
       </c>
       <c r="D78" s="12">
-        <f>SUM(D$7:D16)</f>
+        <f>SUM(D$8:D16)</f>
         <v/>
       </c>
       <c r="E78" s="12">
-        <f>SUM(E$7:E16)</f>
+        <f>SUM(E$8:E16)</f>
         <v/>
       </c>
       <c r="F78" s="12">
-        <f>SUM(F$7:F16)</f>
+        <f>SUM(F$8:F16)</f>
         <v/>
       </c>
       <c r="G78" s="12">
-        <f>SUM(G$7:G16)</f>
+        <f>SUM(G$8:G16)</f>
         <v/>
       </c>
     </row>
@@ -10263,27 +10241,27 @@
         <v/>
       </c>
       <c r="B79" s="12">
-        <f>SUM(B$7:B17)</f>
+        <f>SUM(B$8:B17)</f>
         <v/>
       </c>
       <c r="C79" s="12">
-        <f>SUM(C$7:C17)</f>
+        <f>SUM(C$8:C17)</f>
         <v/>
       </c>
       <c r="D79" s="12">
-        <f>SUM(D$7:D17)</f>
+        <f>SUM(D$8:D17)</f>
         <v/>
       </c>
       <c r="E79" s="12">
-        <f>SUM(E$7:E17)</f>
+        <f>SUM(E$8:E17)</f>
         <v/>
       </c>
       <c r="F79" s="12">
-        <f>SUM(F$7:F17)</f>
+        <f>SUM(F$8:F17)</f>
         <v/>
       </c>
       <c r="G79" s="12">
-        <f>SUM(G$7:G17)</f>
+        <f>SUM(G$8:G17)</f>
         <v/>
       </c>
     </row>
@@ -10293,27 +10271,27 @@
         <v/>
       </c>
       <c r="B80" s="12">
-        <f>SUM(B$7:B18)</f>
+        <f>SUM(B$8:B18)</f>
         <v/>
       </c>
       <c r="C80" s="12">
-        <f>SUM(C$7:C18)</f>
+        <f>SUM(C$8:C18)</f>
         <v/>
       </c>
       <c r="D80" s="12">
-        <f>SUM(D$7:D18)</f>
+        <f>SUM(D$8:D18)</f>
         <v/>
       </c>
       <c r="E80" s="12">
-        <f>SUM(E$7:E18)</f>
+        <f>SUM(E$8:E18)</f>
         <v/>
       </c>
       <c r="F80" s="12">
-        <f>SUM(F$7:F18)</f>
+        <f>SUM(F$8:F18)</f>
         <v/>
       </c>
       <c r="G80" s="12">
-        <f>SUM(G$7:G18)</f>
+        <f>SUM(G$8:G18)</f>
         <v/>
       </c>
     </row>
@@ -10323,27 +10301,27 @@
         <v/>
       </c>
       <c r="B81" s="12">
-        <f>SUM(B$7:B19)</f>
+        <f>SUM(B$8:B19)</f>
         <v/>
       </c>
       <c r="C81" s="12">
-        <f>SUM(C$7:C19)</f>
+        <f>SUM(C$8:C19)</f>
         <v/>
       </c>
       <c r="D81" s="12">
-        <f>SUM(D$7:D19)</f>
+        <f>SUM(D$8:D19)</f>
         <v/>
       </c>
       <c r="E81" s="12">
-        <f>SUM(E$7:E19)</f>
+        <f>SUM(E$8:E19)</f>
         <v/>
       </c>
       <c r="F81" s="12">
-        <f>SUM(F$7:F19)</f>
+        <f>SUM(F$8:F19)</f>
         <v/>
       </c>
       <c r="G81" s="12">
-        <f>SUM(G$7:G19)</f>
+        <f>SUM(G$8:G19)</f>
         <v/>
       </c>
     </row>
@@ -10353,27 +10331,27 @@
         <v/>
       </c>
       <c r="B82" s="12">
-        <f>SUM(B$7:B20)</f>
+        <f>SUM(B$8:B20)</f>
         <v/>
       </c>
       <c r="C82" s="12">
-        <f>SUM(C$7:C20)</f>
+        <f>SUM(C$8:C20)</f>
         <v/>
       </c>
       <c r="D82" s="12">
-        <f>SUM(D$7:D20)</f>
+        <f>SUM(D$8:D20)</f>
         <v/>
       </c>
       <c r="E82" s="12">
-        <f>SUM(E$7:E20)</f>
+        <f>SUM(E$8:E20)</f>
         <v/>
       </c>
       <c r="F82" s="12">
-        <f>SUM(F$7:F20)</f>
+        <f>SUM(F$8:F20)</f>
         <v/>
       </c>
       <c r="G82" s="12">
-        <f>SUM(G$7:G20)</f>
+        <f>SUM(G$8:G20)</f>
         <v/>
       </c>
     </row>
@@ -10383,27 +10361,27 @@
         <v/>
       </c>
       <c r="B83" s="12">
-        <f>SUM(B$7:B21)</f>
+        <f>SUM(B$8:B21)</f>
         <v/>
       </c>
       <c r="C83" s="12">
-        <f>SUM(C$7:C21)</f>
+        <f>SUM(C$8:C21)</f>
         <v/>
       </c>
       <c r="D83" s="12">
-        <f>SUM(D$7:D21)</f>
+        <f>SUM(D$8:D21)</f>
         <v/>
       </c>
       <c r="E83" s="12">
-        <f>SUM(E$7:E21)</f>
+        <f>SUM(E$8:E21)</f>
         <v/>
       </c>
       <c r="F83" s="12">
-        <f>SUM(F$7:F21)</f>
+        <f>SUM(F$8:F21)</f>
         <v/>
       </c>
       <c r="G83" s="12">
-        <f>SUM(G$7:G21)</f>
+        <f>SUM(G$8:G21)</f>
         <v/>
       </c>
     </row>
@@ -10413,27 +10391,27 @@
         <v/>
       </c>
       <c r="B84" s="12">
-        <f>SUM(B$7:B22)</f>
+        <f>SUM(B$8:B22)</f>
         <v/>
       </c>
       <c r="C84" s="12">
-        <f>SUM(C$7:C22)</f>
+        <f>SUM(C$8:C22)</f>
         <v/>
       </c>
       <c r="D84" s="12">
-        <f>SUM(D$7:D22)</f>
+        <f>SUM(D$8:D22)</f>
         <v/>
       </c>
       <c r="E84" s="12">
-        <f>SUM(E$7:E22)</f>
+        <f>SUM(E$8:E22)</f>
         <v/>
       </c>
       <c r="F84" s="12">
-        <f>SUM(F$7:F22)</f>
+        <f>SUM(F$8:F22)</f>
         <v/>
       </c>
       <c r="G84" s="12">
-        <f>SUM(G$7:G22)</f>
+        <f>SUM(G$8:G22)</f>
         <v/>
       </c>
     </row>
@@ -10443,27 +10421,27 @@
         <v/>
       </c>
       <c r="B85" s="12">
-        <f>SUM(B$7:B23)</f>
+        <f>SUM(B$8:B23)</f>
         <v/>
       </c>
       <c r="C85" s="12">
-        <f>SUM(C$7:C23)</f>
+        <f>SUM(C$8:C23)</f>
         <v/>
       </c>
       <c r="D85" s="12">
-        <f>SUM(D$7:D23)</f>
+        <f>SUM(D$8:D23)</f>
         <v/>
       </c>
       <c r="E85" s="12">
-        <f>SUM(E$7:E23)</f>
+        <f>SUM(E$8:E23)</f>
         <v/>
       </c>
       <c r="F85" s="12">
-        <f>SUM(F$7:F23)</f>
+        <f>SUM(F$8:F23)</f>
         <v/>
       </c>
       <c r="G85" s="12">
-        <f>SUM(G$7:G23)</f>
+        <f>SUM(G$8:G23)</f>
         <v/>
       </c>
     </row>
@@ -10473,27 +10451,27 @@
         <v/>
       </c>
       <c r="B86" s="12">
-        <f>SUM(B$7:B24)</f>
+        <f>SUM(B$8:B24)</f>
         <v/>
       </c>
       <c r="C86" s="12">
-        <f>SUM(C$7:C24)</f>
+        <f>SUM(C$8:C24)</f>
         <v/>
       </c>
       <c r="D86" s="12">
-        <f>SUM(D$7:D24)</f>
+        <f>SUM(D$8:D24)</f>
         <v/>
       </c>
       <c r="E86" s="12">
-        <f>SUM(E$7:E24)</f>
+        <f>SUM(E$8:E24)</f>
         <v/>
       </c>
       <c r="F86" s="12">
-        <f>SUM(F$7:F24)</f>
+        <f>SUM(F$8:F24)</f>
         <v/>
       </c>
       <c r="G86" s="12">
-        <f>SUM(G$7:G24)</f>
+        <f>SUM(G$8:G24)</f>
         <v/>
       </c>
     </row>
@@ -10503,27 +10481,27 @@
         <v/>
       </c>
       <c r="B87" s="12">
-        <f>SUM(B$7:B25)</f>
+        <f>SUM(B$8:B25)</f>
         <v/>
       </c>
       <c r="C87" s="12">
-        <f>SUM(C$7:C25)</f>
+        <f>SUM(C$8:C25)</f>
         <v/>
       </c>
       <c r="D87" s="12">
-        <f>SUM(D$7:D25)</f>
+        <f>SUM(D$8:D25)</f>
         <v/>
       </c>
       <c r="E87" s="12">
-        <f>SUM(E$7:E25)</f>
+        <f>SUM(E$8:E25)</f>
         <v/>
       </c>
       <c r="F87" s="12">
-        <f>SUM(F$7:F25)</f>
+        <f>SUM(F$8:F25)</f>
         <v/>
       </c>
       <c r="G87" s="12">
-        <f>SUM(G$7:G25)</f>
+        <f>SUM(G$8:G25)</f>
         <v/>
       </c>
     </row>
@@ -10533,27 +10511,27 @@
         <v/>
       </c>
       <c r="B88" s="12">
-        <f>SUM(B$7:B26)</f>
+        <f>SUM(B$8:B26)</f>
         <v/>
       </c>
       <c r="C88" s="12">
-        <f>SUM(C$7:C26)</f>
+        <f>SUM(C$8:C26)</f>
         <v/>
       </c>
       <c r="D88" s="12">
-        <f>SUM(D$7:D26)</f>
+        <f>SUM(D$8:D26)</f>
         <v/>
       </c>
       <c r="E88" s="12">
-        <f>SUM(E$7:E26)</f>
+        <f>SUM(E$8:E26)</f>
         <v/>
       </c>
       <c r="F88" s="12">
-        <f>SUM(F$7:F26)</f>
+        <f>SUM(F$8:F26)</f>
         <v/>
       </c>
       <c r="G88" s="12">
-        <f>SUM(G$7:G26)</f>
+        <f>SUM(G$8:G26)</f>
         <v/>
       </c>
     </row>
@@ -10563,27 +10541,27 @@
         <v/>
       </c>
       <c r="B89" s="12">
-        <f>SUM(B$7:B27)</f>
+        <f>SUM(B$8:B27)</f>
         <v/>
       </c>
       <c r="C89" s="12">
-        <f>SUM(C$7:C27)</f>
+        <f>SUM(C$8:C27)</f>
         <v/>
       </c>
       <c r="D89" s="12">
-        <f>SUM(D$7:D27)</f>
+        <f>SUM(D$8:D27)</f>
         <v/>
       </c>
       <c r="E89" s="12">
-        <f>SUM(E$7:E27)</f>
+        <f>SUM(E$8:E27)</f>
         <v/>
       </c>
       <c r="F89" s="12">
-        <f>SUM(F$7:F27)</f>
+        <f>SUM(F$8:F27)</f>
         <v/>
       </c>
       <c r="G89" s="12">
-        <f>SUM(G$7:G27)</f>
+        <f>SUM(G$8:G27)</f>
         <v/>
       </c>
     </row>
@@ -10593,27 +10571,27 @@
         <v/>
       </c>
       <c r="B90" s="12">
-        <f>SUM(B$7:B28)</f>
+        <f>SUM(B$8:B28)</f>
         <v/>
       </c>
       <c r="C90" s="12">
-        <f>SUM(C$7:C28)</f>
+        <f>SUM(C$8:C28)</f>
         <v/>
       </c>
       <c r="D90" s="12">
-        <f>SUM(D$7:D28)</f>
+        <f>SUM(D$8:D28)</f>
         <v/>
       </c>
       <c r="E90" s="12">
-        <f>SUM(E$7:E28)</f>
+        <f>SUM(E$8:E28)</f>
         <v/>
       </c>
       <c r="F90" s="12">
-        <f>SUM(F$7:F28)</f>
+        <f>SUM(F$8:F28)</f>
         <v/>
       </c>
       <c r="G90" s="12">
-        <f>SUM(G$7:G28)</f>
+        <f>SUM(G$8:G28)</f>
         <v/>
       </c>
     </row>
@@ -10623,27 +10601,27 @@
         <v/>
       </c>
       <c r="B91" s="12">
-        <f>SUM(B$7:B29)</f>
+        <f>SUM(B$8:B29)</f>
         <v/>
       </c>
       <c r="C91" s="12">
-        <f>SUM(C$7:C29)</f>
+        <f>SUM(C$8:C29)</f>
         <v/>
       </c>
       <c r="D91" s="12">
-        <f>SUM(D$7:D29)</f>
+        <f>SUM(D$8:D29)</f>
         <v/>
       </c>
       <c r="E91" s="12">
-        <f>SUM(E$7:E29)</f>
+        <f>SUM(E$8:E29)</f>
         <v/>
       </c>
       <c r="F91" s="12">
-        <f>SUM(F$7:F29)</f>
+        <f>SUM(F$8:F29)</f>
         <v/>
       </c>
       <c r="G91" s="12">
-        <f>SUM(G$7:G29)</f>
+        <f>SUM(G$8:G29)</f>
         <v/>
       </c>
     </row>
@@ -10653,27 +10631,27 @@
         <v/>
       </c>
       <c r="B92" s="12">
-        <f>SUM(B$7:B30)</f>
+        <f>SUM(B$8:B30)</f>
         <v/>
       </c>
       <c r="C92" s="12">
-        <f>SUM(C$7:C30)</f>
+        <f>SUM(C$8:C30)</f>
         <v/>
       </c>
       <c r="D92" s="12">
-        <f>SUM(D$7:D30)</f>
+        <f>SUM(D$8:D30)</f>
         <v/>
       </c>
       <c r="E92" s="12">
-        <f>SUM(E$7:E30)</f>
+        <f>SUM(E$8:E30)</f>
         <v/>
       </c>
       <c r="F92" s="12">
-        <f>SUM(F$7:F30)</f>
+        <f>SUM(F$8:F30)</f>
         <v/>
       </c>
       <c r="G92" s="12">
-        <f>SUM(G$7:G30)</f>
+        <f>SUM(G$8:G30)</f>
         <v/>
       </c>
     </row>
@@ -10683,27 +10661,27 @@
         <v/>
       </c>
       <c r="B93" s="12">
-        <f>SUM(B$7:B31)</f>
+        <f>SUM(B$8:B31)</f>
         <v/>
       </c>
       <c r="C93" s="12">
-        <f>SUM(C$7:C31)</f>
+        <f>SUM(C$8:C31)</f>
         <v/>
       </c>
       <c r="D93" s="12">
-        <f>SUM(D$7:D31)</f>
+        <f>SUM(D$8:D31)</f>
         <v/>
       </c>
       <c r="E93" s="12">
-        <f>SUM(E$7:E31)</f>
+        <f>SUM(E$8:E31)</f>
         <v/>
       </c>
       <c r="F93" s="12">
-        <f>SUM(F$7:F31)</f>
+        <f>SUM(F$8:F31)</f>
         <v/>
       </c>
       <c r="G93" s="12">
-        <f>SUM(G$7:G31)</f>
+        <f>SUM(G$8:G31)</f>
         <v/>
       </c>
     </row>
@@ -10713,27 +10691,27 @@
         <v/>
       </c>
       <c r="B94" s="12">
-        <f>SUM(B$7:B32)</f>
+        <f>SUM(B$8:B32)</f>
         <v/>
       </c>
       <c r="C94" s="12">
-        <f>SUM(C$7:C32)</f>
+        <f>SUM(C$8:C32)</f>
         <v/>
       </c>
       <c r="D94" s="12">
-        <f>SUM(D$7:D32)</f>
+        <f>SUM(D$8:D32)</f>
         <v/>
       </c>
       <c r="E94" s="12">
-        <f>SUM(E$7:E32)</f>
+        <f>SUM(E$8:E32)</f>
         <v/>
       </c>
       <c r="F94" s="12">
-        <f>SUM(F$7:F32)</f>
+        <f>SUM(F$8:F32)</f>
         <v/>
       </c>
       <c r="G94" s="12">
-        <f>SUM(G$7:G32)</f>
+        <f>SUM(G$8:G32)</f>
         <v/>
       </c>
     </row>
@@ -10743,27 +10721,27 @@
         <v/>
       </c>
       <c r="B95" s="12">
-        <f>SUM(B$7:B33)</f>
+        <f>SUM(B$8:B33)</f>
         <v/>
       </c>
       <c r="C95" s="12">
-        <f>SUM(C$7:C33)</f>
+        <f>SUM(C$8:C33)</f>
         <v/>
       </c>
       <c r="D95" s="12">
-        <f>SUM(D$7:D33)</f>
+        <f>SUM(D$8:D33)</f>
         <v/>
       </c>
       <c r="E95" s="12">
-        <f>SUM(E$7:E33)</f>
+        <f>SUM(E$8:E33)</f>
         <v/>
       </c>
       <c r="F95" s="12">
-        <f>SUM(F$7:F33)</f>
+        <f>SUM(F$8:F33)</f>
         <v/>
       </c>
       <c r="G95" s="12">
-        <f>SUM(G$7:G33)</f>
+        <f>SUM(G$8:G33)</f>
         <v/>
       </c>
     </row>
@@ -10773,27 +10751,27 @@
         <v/>
       </c>
       <c r="B96" s="12">
-        <f>SUM(B$7:B34)</f>
+        <f>SUM(B$8:B34)</f>
         <v/>
       </c>
       <c r="C96" s="12">
-        <f>SUM(C$7:C34)</f>
+        <f>SUM(C$8:C34)</f>
         <v/>
       </c>
       <c r="D96" s="12">
-        <f>SUM(D$7:D34)</f>
+        <f>SUM(D$8:D34)</f>
         <v/>
       </c>
       <c r="E96" s="12">
-        <f>SUM(E$7:E34)</f>
+        <f>SUM(E$8:E34)</f>
         <v/>
       </c>
       <c r="F96" s="12">
-        <f>SUM(F$7:F34)</f>
+        <f>SUM(F$8:F34)</f>
         <v/>
       </c>
       <c r="G96" s="12">
-        <f>SUM(G$7:G34)</f>
+        <f>SUM(G$8:G34)</f>
         <v/>
       </c>
     </row>
@@ -10803,27 +10781,27 @@
         <v/>
       </c>
       <c r="B97" s="12">
-        <f>SUM(B$7:B35)</f>
+        <f>SUM(B$8:B35)</f>
         <v/>
       </c>
       <c r="C97" s="12">
-        <f>SUM(C$7:C35)</f>
+        <f>SUM(C$8:C35)</f>
         <v/>
       </c>
       <c r="D97" s="12">
-        <f>SUM(D$7:D35)</f>
+        <f>SUM(D$8:D35)</f>
         <v/>
       </c>
       <c r="E97" s="12">
-        <f>SUM(E$7:E35)</f>
+        <f>SUM(E$8:E35)</f>
         <v/>
       </c>
       <c r="F97" s="12">
-        <f>SUM(F$7:F35)</f>
+        <f>SUM(F$8:F35)</f>
         <v/>
       </c>
       <c r="G97" s="12">
-        <f>SUM(G$7:G35)</f>
+        <f>SUM(G$8:G35)</f>
         <v/>
       </c>
     </row>
@@ -10833,27 +10811,27 @@
         <v/>
       </c>
       <c r="B98" s="12">
-        <f>SUM(B$7:B36)</f>
+        <f>SUM(B$8:B36)</f>
         <v/>
       </c>
       <c r="C98" s="12">
-        <f>SUM(C$7:C36)</f>
+        <f>SUM(C$8:C36)</f>
         <v/>
       </c>
       <c r="D98" s="12">
-        <f>SUM(D$7:D36)</f>
+        <f>SUM(D$8:D36)</f>
         <v/>
       </c>
       <c r="E98" s="12">
-        <f>SUM(E$7:E36)</f>
+        <f>SUM(E$8:E36)</f>
         <v/>
       </c>
       <c r="F98" s="12">
-        <f>SUM(F$7:F36)</f>
+        <f>SUM(F$8:F36)</f>
         <v/>
       </c>
       <c r="G98" s="12">
-        <f>SUM(G$7:G36)</f>
+        <f>SUM(G$8:G36)</f>
         <v/>
       </c>
     </row>
@@ -10863,27 +10841,27 @@
         <v/>
       </c>
       <c r="B99" s="12">
-        <f>SUM(B$7:B37)</f>
+        <f>SUM(B$8:B37)</f>
         <v/>
       </c>
       <c r="C99" s="12">
-        <f>SUM(C$7:C37)</f>
+        <f>SUM(C$8:C37)</f>
         <v/>
       </c>
       <c r="D99" s="12">
-        <f>SUM(D$7:D37)</f>
+        <f>SUM(D$8:D37)</f>
         <v/>
       </c>
       <c r="E99" s="12">
-        <f>SUM(E$7:E37)</f>
+        <f>SUM(E$8:E37)</f>
         <v/>
       </c>
       <c r="F99" s="12">
-        <f>SUM(F$7:F37)</f>
+        <f>SUM(F$8:F37)</f>
         <v/>
       </c>
       <c r="G99" s="12">
-        <f>SUM(G$7:G37)</f>
+        <f>SUM(G$8:G37)</f>
         <v/>
       </c>
     </row>
@@ -10893,27 +10871,27 @@
         <v/>
       </c>
       <c r="B100" s="12">
-        <f>SUM(B$7:B38)</f>
+        <f>SUM(B$8:B38)</f>
         <v/>
       </c>
       <c r="C100" s="12">
-        <f>SUM(C$7:C38)</f>
+        <f>SUM(C$8:C38)</f>
         <v/>
       </c>
       <c r="D100" s="12">
-        <f>SUM(D$7:D38)</f>
+        <f>SUM(D$8:D38)</f>
         <v/>
       </c>
       <c r="E100" s="12">
-        <f>SUM(E$7:E38)</f>
+        <f>SUM(E$8:E38)</f>
         <v/>
       </c>
       <c r="F100" s="12">
-        <f>SUM(F$7:F38)</f>
+        <f>SUM(F$8:F38)</f>
         <v/>
       </c>
       <c r="G100" s="12">
-        <f>SUM(G$7:G38)</f>
+        <f>SUM(G$8:G38)</f>
         <v/>
       </c>
     </row>
@@ -10923,27 +10901,27 @@
         <v/>
       </c>
       <c r="B101" s="12">
-        <f>SUM(B$7:B39)</f>
+        <f>SUM(B$8:B39)</f>
         <v/>
       </c>
       <c r="C101" s="12">
-        <f>SUM(C$7:C39)</f>
+        <f>SUM(C$8:C39)</f>
         <v/>
       </c>
       <c r="D101" s="12">
-        <f>SUM(D$7:D39)</f>
+        <f>SUM(D$8:D39)</f>
         <v/>
       </c>
       <c r="E101" s="12">
-        <f>SUM(E$7:E39)</f>
+        <f>SUM(E$8:E39)</f>
         <v/>
       </c>
       <c r="F101" s="12">
-        <f>SUM(F$7:F39)</f>
+        <f>SUM(F$8:F39)</f>
         <v/>
       </c>
       <c r="G101" s="12">
-        <f>SUM(G$7:G39)</f>
+        <f>SUM(G$8:G39)</f>
         <v/>
       </c>
     </row>
@@ -10953,27 +10931,27 @@
         <v/>
       </c>
       <c r="B102" s="12">
-        <f>SUM(B$7:B40)</f>
+        <f>SUM(B$8:B40)</f>
         <v/>
       </c>
       <c r="C102" s="12">
-        <f>SUM(C$7:C40)</f>
+        <f>SUM(C$8:C40)</f>
         <v/>
       </c>
       <c r="D102" s="12">
-        <f>SUM(D$7:D40)</f>
+        <f>SUM(D$8:D40)</f>
         <v/>
       </c>
       <c r="E102" s="12">
-        <f>SUM(E$7:E40)</f>
+        <f>SUM(E$8:E40)</f>
         <v/>
       </c>
       <c r="F102" s="12">
-        <f>SUM(F$7:F40)</f>
+        <f>SUM(F$8:F40)</f>
         <v/>
       </c>
       <c r="G102" s="12">
-        <f>SUM(G$7:G40)</f>
+        <f>SUM(G$8:G40)</f>
         <v/>
       </c>
     </row>
@@ -10983,27 +10961,27 @@
         <v/>
       </c>
       <c r="B103" s="12">
-        <f>SUM(B$7:B41)</f>
+        <f>SUM(B$8:B41)</f>
         <v/>
       </c>
       <c r="C103" s="12">
-        <f>SUM(C$7:C41)</f>
+        <f>SUM(C$8:C41)</f>
         <v/>
       </c>
       <c r="D103" s="12">
-        <f>SUM(D$7:D41)</f>
+        <f>SUM(D$8:D41)</f>
         <v/>
       </c>
       <c r="E103" s="12">
-        <f>SUM(E$7:E41)</f>
+        <f>SUM(E$8:E41)</f>
         <v/>
       </c>
       <c r="F103" s="12">
-        <f>SUM(F$7:F41)</f>
+        <f>SUM(F$8:F41)</f>
         <v/>
       </c>
       <c r="G103" s="12">
-        <f>SUM(G$7:G41)</f>
+        <f>SUM(G$8:G41)</f>
         <v/>
       </c>
     </row>
@@ -11013,629 +10991,686 @@
         <v/>
       </c>
       <c r="B104" s="12">
-        <f>SUM(B$7:B42)</f>
+        <f>SUM(B$8:B42)</f>
         <v/>
       </c>
       <c r="C104" s="12">
-        <f>SUM(C$7:C42)</f>
+        <f>SUM(C$8:C42)</f>
         <v/>
       </c>
       <c r="D104" s="12">
-        <f>SUM(D$7:D42)</f>
+        <f>SUM(D$8:D42)</f>
         <v/>
       </c>
       <c r="E104" s="12">
-        <f>SUM(E$7:E42)</f>
+        <f>SUM(E$8:E42)</f>
         <v/>
       </c>
       <c r="F104" s="12">
-        <f>SUM(F$7:F42)</f>
+        <f>SUM(F$8:F42)</f>
         <v/>
       </c>
       <c r="G104" s="12">
-        <f>SUM(G$7:G42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+        <f>SUM(G$8:G42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10">
+        <f>A43</f>
+        <v/>
+      </c>
+      <c r="B105" s="12">
+        <f>SUM(B$8:B43)</f>
+        <v/>
+      </c>
+      <c r="C105" s="12">
+        <f>SUM(C$8:C43)</f>
+        <v/>
+      </c>
+      <c r="D105" s="12">
+        <f>SUM(D$8:D43)</f>
+        <v/>
+      </c>
+      <c r="E105" s="12">
+        <f>SUM(E$8:E43)</f>
+        <v/>
+      </c>
+      <c r="F105" s="12">
+        <f>SUM(F$8:F43)</f>
+        <v/>
+      </c>
+      <c r="G105" s="12">
+        <f>SUM(G$8:G43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>■ 段階ごとの誤差(評価するのは まだ確定していない区間だけ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>確定分は実績そのもので誤差0のため、混ぜると段階が進むほど自動的に数字が良くなる。それでは予測が良くなったのか確定が増えただけなのか区別できないので、残り区間だけで測っている。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>「見込んだ総工数」は どの段階でも同じ値になる。総工数は契約人月(または見積もり)で決まっており、実績を確定させても動かないため。確定分が既にそれを超えている段階だけ、実績そのものが下限になって大きくなる。</t>
+          <t>確定分は実績そのもので誤差0のため、混ぜると段階が進むほど自動的に数字が良くなる。それでは予測が良くなったのか確定が増えただけなのか区別できないので、残り区間だけで測っている。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>「残工数の倍率」は 残工数 ÷ 学習カーブが残り区間に置く量。1.0 なら学習カーブどおり。1 より大きいほど確定分が学習カーブより少なく、そのずれが残り区間へ上乗せされる。切り替え点の段差の高さは この倍率そのもの。</t>
+          <t>「見込んだ総工数」は どの段階でも同じ値になる。総工数は契約人月(または見積もり)で決まっており、実績を確定させても動かないため。確定分が既にそれを超えている段階だけ、実績そのものが下限になって大きくなる。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
+          <t>「立上り制約に当たった月数」が 0 でない段階は、学習カーブどおりに配ると立ち上がりが急すぎるため、工数を後ろの月へ送っている。その段階では山が後ろへ移動し、なだらかになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>「残工数の倍率」は 残工数 ÷ 学習カーブが残り区間に置く量。1.0 なら学習カーブどおり。1 より大きいほど確定分が学習カーブより少なく、そのずれが残り区間へ上乗せされる。切り替え点の段差の高さは この倍率そのもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
           <t>終盤の段階ほど残り区間は短く、量も小さい。誤差率はその小さい分母で割った値なので数字が跳ねやすい。「残りが全体に占める割合」を見て、どれだけの量に対する誤差なのかと併せて読むこと。</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>区切り</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C135" s="8" t="inlineStr">
         <is>
           <t>確定した月</t>
         </is>
       </c>
-      <c r="D133" s="8" t="inlineStr">
+      <c r="D135" s="8" t="inlineStr">
         <is>
           <t>確定月数</t>
         </is>
       </c>
-      <c r="E133" s="8" t="inlineStr">
+      <c r="E135" s="8" t="inlineStr">
         <is>
           <t>見込んだ総工数(時間)</t>
         </is>
       </c>
-      <c r="F133" s="8" t="inlineStr">
+      <c r="F135" s="8" t="inlineStr">
         <is>
           <t>残工数の倍率(学習カーブ比)</t>
         </is>
       </c>
-      <c r="G133" s="8" t="inlineStr">
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>立上り制約に当たった月数</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr">
         <is>
           <t>残り月数</t>
         </is>
       </c>
-      <c r="H133" s="8" t="inlineStr">
+      <c r="I135" s="8" t="inlineStr">
         <is>
           <t>評価した月数</t>
         </is>
       </c>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="J135" s="8" t="inlineStr">
         <is>
           <t>残り実績(時間)</t>
         </is>
       </c>
-      <c r="J133" s="8" t="inlineStr">
+      <c r="K135" s="8" t="inlineStr">
         <is>
           <t>残りが全体に占める割合(%)</t>
         </is>
       </c>
-      <c r="K133" s="8" t="inlineStr">
+      <c r="L135" s="8" t="inlineStr">
         <is>
           <t>残り予測(時間)</t>
         </is>
       </c>
-      <c r="L133" s="8" t="inlineStr">
+      <c r="M135" s="8" t="inlineStr">
         <is>
           <t>残り総量誤差(%)</t>
         </is>
       </c>
-      <c r="M133" s="8" t="inlineStr">
+      <c r="N135" s="8" t="inlineStr">
         <is>
           <t>残り月次WAPE</t>
         </is>
       </c>
-      <c r="N133" s="8" t="inlineStr">
+      <c r="O135" s="8" t="inlineStr">
         <is>
           <t>残りピーク月ズレ</t>
         </is>
       </c>
-      <c r="O133" s="8" t="inlineStr">
+      <c r="P135" s="8" t="inlineStr">
         <is>
           <t>累積カーブ最大乖離</t>
         </is>
       </c>
-      <c r="P133" s="8" t="inlineStr">
+      <c r="Q135" s="8" t="inlineStr">
         <is>
           <t>総量誤差(%)</t>
         </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="B134" s="10" t="inlineStr">
-        <is>
-          <t>(なし)</t>
-        </is>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
-        <is>
-          <t>(なし)</t>
-        </is>
-      </c>
-      <c r="D134" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="12" t="n">
-        <v>472000</v>
-      </c>
-      <c r="F134" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="H134" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="I134" s="12" t="n">
-        <v>482150.4</v>
-      </c>
-      <c r="J134" s="24" t="n">
-        <v>100</v>
-      </c>
-      <c r="K134" s="12" t="n">
-        <v>472000</v>
-      </c>
-      <c r="L134" s="24" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>0.3642</v>
-      </c>
-      <c r="N134" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O134" s="22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="P134" s="24" t="n">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E135" s="12" t="n">
-        <v>472000</v>
-      </c>
-      <c r="F135" s="23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G135" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="H135" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="I135" s="12" t="n">
-        <v>420709.6</v>
-      </c>
-      <c r="J135" s="24" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="K135" s="12" t="n">
-        <v>410559.2</v>
-      </c>
-      <c r="L135" s="24" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="M135" s="22" t="n">
-        <v>0.3866</v>
-      </c>
-      <c r="N135" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O135" s="22" t="n">
-        <v>0.1659</v>
-      </c>
-      <c r="P135" s="24" t="n">
-        <v>-2.1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>α版</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>472000</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G136" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H136" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="I136" s="12" t="n">
-        <v>255714.2</v>
-      </c>
-      <c r="J136" s="24" t="n">
-        <v>53</v>
-      </c>
-      <c r="K136" s="12" t="n">
-        <v>245563.8</v>
-      </c>
-      <c r="L136" s="24" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M136" s="22" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="N136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O136" s="22" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="P136" s="24" t="n">
+      <c r="H136" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I136" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="J136" s="12" t="n">
+        <v>482150.4</v>
+      </c>
+      <c r="K136" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L136" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="M136" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="N136" s="22" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="O136" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P136" s="22" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q136" s="24" t="n">
         <v>-2.1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>β版</t>
+          <t>プロトタイプ</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E137" s="12" t="n">
         <v>472000</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G137" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H137" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I137" s="12" t="n">
-        <v>75222</v>
-      </c>
-      <c r="J137" s="24" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K137" s="12" t="n">
-        <v>65071.6</v>
-      </c>
-      <c r="L137" s="24" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>0.3871</v>
-      </c>
-      <c r="N137" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G137" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O137" s="22" t="n">
-        <v>0.0206</v>
-      </c>
-      <c r="P137" s="24" t="n">
+      <c r="H137" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I137" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J137" s="12" t="n">
+        <v>420709.6</v>
+      </c>
+      <c r="K137" s="24" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="L137" s="12" t="n">
+        <v>410559.2</v>
+      </c>
+      <c r="M137" s="24" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="O137" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P137" s="22" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="Q137" s="24" t="n">
         <v>-2.1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>マスターアップ</t>
+          <t>α版</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E138" s="12" t="n">
         <v>472000</v>
       </c>
       <c r="F138" s="23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G138" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I138" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J138" s="12" t="n">
+        <v>255714.2</v>
+      </c>
+      <c r="K138" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="L138" s="12" t="n">
+        <v>245563.8</v>
+      </c>
+      <c r="M138" s="24" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N138" s="22" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="O138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="22" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="Q138" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>β版</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="F139" s="23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G139" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I139" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J139" s="12" t="n">
+        <v>75222</v>
+      </c>
+      <c r="K139" s="24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L139" s="12" t="n">
+        <v>65071.6</v>
+      </c>
+      <c r="M139" s="24" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="N139" s="22" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="O139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="22" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="Q139" s="24" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>マスターアップ</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E140" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="F140" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="G138" s="10" t="n">
+      <c r="G140" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H138" s="11" t="n">
+      <c r="I140" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="I138" s="12" t="n">
+      <c r="J140" s="12" t="n">
         <v>11869.4</v>
       </c>
-      <c r="J138" s="24" t="n">
+      <c r="K140" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="K138" s="12" t="n">
+      <c r="L140" s="12" t="n">
         <v>1719</v>
       </c>
-      <c r="L138" s="24" t="n">
+      <c r="M140" s="24" t="n">
         <v>-85.5</v>
       </c>
-      <c r="M138" s="22" t="n">
+      <c r="N140" s="22" t="n">
         <v>0.8552</v>
       </c>
-      <c r="N138" s="10" t="n">
+      <c r="O140" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O138" s="22" t="n">
+      <c r="P140" s="22" t="n">
         <v>0.021</v>
       </c>
-      <c r="P138" s="24" t="n">
+      <c r="Q140" s="24" t="n">
         <v>-2.1</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
         <is>
           <t>■ 各段階の条件</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="25" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="25" t="inlineStr">
         <is>
           <t>段階0 着手前</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・実績を一切使わない全期間予測。マイルストーンの日付も使っていない(着手前に通過済みのマイルストーンは無いため)。「予測」シートは記入済みの日付をすべて使うので、その分だけ条件が違う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・実績を一切使わない全期間予測。マイルストーンの日付も使っていない(着手前に通過済みのマイルストーンは無いため)。「予測」シートは記入済みの日付をすべて使うので、その分だけ条件が違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・マイルストーンの指定が無いため、学習カーブをそのまま期間に貼っています。</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="25" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="25" t="inlineStr">
         <is>
           <t>段階1 プロトタイプ後(2021-10まで確定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2021-01〜2021-10 の 10 ヶ月を実績で確定し、残り 26 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+          <t xml:space="preserve">  ・2021-01〜2021-10 の 10 ヶ月を実績で確定し、残り 26 ヶ月を予測している。</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・マイルストーンの指定が無いため、学習カーブをそのまま期間に貼っています。</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="25" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="25" t="inlineStr">
         <is>
           <t>段階2 α版後(2022-04まで確定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2021-01〜2022-04 の 16 ヶ月を実績で確定し、残り 20 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+          <t xml:space="preserve">  ・2021-01〜2022-04 の 16 ヶ月を実績で確定し、残り 20 ヶ月を予測している。</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版</t>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: 企画・プリプロ(計 9,390 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="25" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="25" t="inlineStr">
         <is>
           <t>段階3 β版後(2023-03まで確定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2021-01〜2023-03 の 27 ヶ月を実績で確定し、残り 9 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+          <t xml:space="preserve">  ・2021-01〜2023-03 の 27 ヶ月を実績で確定し、残り 9 ヶ月を予測している。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版</t>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・確定分の実績が学習カーブの見込みより多いため、残り区間に配る工数が学習カーブの 0.65 倍になっている。総工数は動かさない決まりなので、そのずれは残り区間へ寄せるほかなく、2023-03 の直後に下へ段差が出る。この案件は学習した消化ペースから外れている、と読むこと。</t>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・確定分の実績が学習カーブの見込みより多いため、残り区間に配る工数が学習カーブの 0.65 倍になっている。総工数は動かさない決まりなので、そのずれは残り区間へ寄せるほかなく、2023-03 の直後に下へ段差が出る。この案件は学習した消化ペースから外れている、と読むこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: ゲームデザイン・シナリオ, 企画・プリプロ(計 16,539 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="25" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="25" t="inlineStr">
         <is>
           <t>段階4 マスターアップ後(2023-08まで確定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・2021-01〜2023-08 の 32 ヶ月を実績で確定し、残り 4 ヶ月を予測している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ, マスターアップ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
+          <t xml:space="preserve">  ・2021-01〜2023-08 の 32 ヶ月を実績で確定し、残り 4 ヶ月を予測している。</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版, マスターアップ</t>
+          <t xml:space="preserve">  ・使うマイルストーンは通過済みのものだけ: α版, β版, プロトタイプ, マスターアップ。先のマイルストーンの日付はその時点では分かっていないため渡さず、学習した平均位置を使う(渡すと未来を覗いた予測になり評価にならない)。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・確定分の実績が学習カーブの見込みより多いため、残り区間に配る工数が学習カーブの 0.10 倍になっている。総工数は動かさない決まりなので、そのずれは残り区間へ寄せるほかなく、2023-08 の直後に下へ段差が出る。この案件は学習した消化ペースから外れている、と読むこと。</t>
+          <t xml:space="preserve">  ・行程グループ間の総量は学習した工数比率で配分しています。</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: アート, ゲームデザイン・シナリオ, サウンド, 企画・プリプロ(計 26,650 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
+          <t xml:space="preserve">  ・指定されたマイルストーンで時間軸を固定: α版, β版, マスターアップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・確定分の実績が学習カーブの見込みより多いため、残り区間に配る工数が学習カーブの 0.10 倍になっている。総工数は動かさない決まりなので、そのずれは残り区間へ寄せるほかなく、2023-08 の直後に下へ段差が出る。この案件は学習した消化ペースから外れている、と読むこと。</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・確定分が見込み総量を超えている行程グループ: アート, ゲームデザイン・シナリオ, サウンド, 企画・プリプロ(計 26,650 時間の超過)。その超過は、まだ残っているグループの残工数から差し引いている(案件全体の総工数を動かさないため)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
         <is>
           <t>※ PJ-2021-E は完了案件として学習データに入っているため、段階予測では自分自身を学習から外した 9 件で学習し直している(自分の実績で学習したカーブで自分を予測すると評価にならない)。</t>
         </is>
@@ -77491,7 +77526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -77548,7 +77583,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:20:38</t>
+          <t>2026-09-04 00:45:20</t>
         </is>
       </c>
     </row>
@@ -77761,427 +77796,404 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>実装範囲</t>
+          <t>立ち上がり上限</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>実装順序 1〜2(素朴版 + マイルストーン位置合わせ) + 見積もりによる総量指定</t>
+          <t>1.33 倍/月(段階予測のみ)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>実装範囲</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>実装順序 1〜2(素朴版 + マイルストーン位置合わせ) + 見積もりによる総量指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>未使用パラメータ</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>k=3.0, タグ重み係数=0.5 (実装順序 3・4 で使用予定)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>■ 人月換算</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>換算係数</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B30" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>時間 / 人月</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>人月の定義は組織によって揺れる。この係数を明記しないまま数字が独り歩きすると議論が噛み合わなくなる(設計書 4-3)。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>■ 学習に使用した案件と重み</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>第1版(素朴版+位置合わせ)では全案件の重みを 1.0 で固定している。種別・タグによる重み付けは実装順序 3・4 で導入する。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>案件ID</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>重み</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>契約人月</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>実績人月</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>乖離率(%)</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>期間(月)</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>マイルストーン数</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2019-A</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>蒼穹のレガリア</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>新規タイトル開発</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>2372.3</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>PJ-2020-B</t>
+          <t>PJ-2019-A</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>ブレイブフロンティア外伝(後半集中)</t>
+          <t>蒼穹のレガリア</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>大型アップデート</t>
+          <t>新規タイトル開発</t>
         </is>
       </c>
       <c r="D36" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>620</v>
+        <v>2400</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>625.1</v>
+        <v>2372.3</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PJ-2020-C</t>
+          <t>PJ-2020-B</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>クロノスギア(二山)</t>
+          <t>ブレイブフロンティア外伝(後半集中)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>新規タイトル開発</t>
+          <t>大型アップデート</t>
         </is>
       </c>
       <c r="D37" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1800</v>
+        <v>620</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>1806.5</v>
+        <v>625.1</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>PJ-2021-D</t>
+          <t>PJ-2020-C</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>蒼穹のレガリア HD Edition(前倒し)</t>
+          <t>クロノスギア(二山)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>移植・リマスター</t>
+          <t>新規タイトル開発</t>
         </is>
       </c>
       <c r="D38" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>520</v>
+        <v>1800</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>518.2</v>
+        <v>1806.5</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PJ-2021-E</t>
+          <t>PJ-2021-D</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>シャドウヴェイル</t>
+          <t>蒼穹のレガリア HD Edition(前倒し)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>新規タイトル開発</t>
+          <t>移植・リマスター</t>
         </is>
       </c>
       <c r="D39" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>2950</v>
+        <v>520</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>3013.4</v>
+        <v>518.2</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>2.2</v>
+        <v>-0.3</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>PJ-2022-F</t>
+          <t>PJ-2021-E</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>ネオンハーツ Season2</t>
+          <t>シャドウヴェイル</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>大型アップデート</t>
+          <t>新規タイトル開発</t>
         </is>
       </c>
       <c r="D40" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>880</v>
+        <v>2950</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>881.8</v>
+        <v>3013.4</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PJ-2022-G</t>
+          <t>PJ-2022-F</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>ギルドマスターズ(前倒し)</t>
+          <t>ネオンハーツ Season2</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>新規タイトル開発</t>
+          <t>大型アップデート</t>
         </is>
       </c>
       <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>1450</v>
+        <v>880</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1461</v>
+        <v>881.8</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>PJ-2023-H</t>
+          <t>PJ-2022-G</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>クロノスギア:蒼き遺産</t>
+          <t>ギルドマスターズ(前倒し)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>大型アップデート</t>
+          <t>新規タイトル開発</t>
         </is>
       </c>
       <c r="D42" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>1100</v>
+        <v>1450</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>1104.9</v>
+        <v>1461</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PJ-2023-I</t>
+          <t>PJ-2023-H</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>ブレイブフロンティア Remaster</t>
+          <t>クロノスギア:蒼き遺産</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>移植・リマスター</t>
+          <t>大型アップデート</t>
         </is>
       </c>
       <c r="D43" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>709.7</v>
+        <v>1104.9</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>3</v>
@@ -78190,652 +78202,666 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>PJ-2024-J</t>
+          <t>PJ-2023-I</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>オーヴァーロード・サーガ(後半集中)</t>
+          <t>ブレイブフロンティア Remaster</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>新規タイトル開発</t>
+          <t>移植・リマスター</t>
         </is>
       </c>
       <c r="D44" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>709.7</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2024-J</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>オーヴァーロード・サーガ(後半集中)</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>新規タイトル開発</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="12" t="n">
         <v>2200</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>2162.6</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G45" s="10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H44" s="10" t="n">
+      <c r="H45" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I45" s="10" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>■ 案件別 × 行程グループ 実績工数(人月)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>予測と同じ集計(phase_map に載る行程・契約期間内)での実績合計。0 はその案件がその業務を行っていないことを示す。最下行は全案件の合計で、その構成比が学習値そのものではない点に注意(学習は案件ごとの構成比を平均するため、規模の大きい案件に引っ張られない)。</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>案件ID</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>期間(月)</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>企画・プリプロ</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>ゲームデザイン・シナリオ</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>プログラム</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>アート</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>サウンド</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>QA・デバッグ</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>PM・運営</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2019-A</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>蒼穹のレガリア</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="D50" s="19" t="n">
-        <v>185</v>
-      </c>
-      <c r="E50" s="19" t="n">
-        <v>297.4</v>
-      </c>
-      <c r="F50" s="19" t="n">
-        <v>589.6</v>
-      </c>
-      <c r="G50" s="19" t="n">
-        <v>772.4</v>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>119.1</v>
-      </c>
-      <c r="I50" s="19" t="n">
-        <v>272.4</v>
-      </c>
-      <c r="J50" s="19" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="K50" s="19" t="n">
-        <v>2372.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PJ-2020-B</t>
+          <t>PJ-2019-A</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>ブレイブフロンティア外伝(後半集中)</t>
+          <t>蒼穹のレガリア</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D51" s="19" t="n">
-        <v>40.2</v>
+        <v>185</v>
       </c>
       <c r="E51" s="19" t="n">
-        <v>85.5</v>
+        <v>297.4</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>145.7</v>
+        <v>589.6</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>202.1</v>
+        <v>772.4</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>25.6</v>
+        <v>119.1</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>87.59999999999999</v>
+        <v>272.4</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>38.5</v>
+        <v>136.4</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>625.1</v>
+        <v>2372.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>PJ-2020-C</t>
+          <t>PJ-2020-B</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>クロノスギア(二山)</t>
+          <t>ブレイブフロンティア外伝(後半集中)</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D52" s="19" t="n">
-        <v>141.4</v>
+        <v>40.2</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>217.4</v>
+        <v>85.5</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>502.4</v>
+        <v>145.7</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>524.6</v>
+        <v>202.1</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>87.40000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>225.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J52" s="19" t="n">
-        <v>108.2</v>
+        <v>38.5</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>1806.5</v>
+        <v>625.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PJ-2021-D</t>
+          <t>PJ-2020-C</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>蒼穹のレガリア HD Edition(前倒し)</t>
+          <t>クロノスギア(二山)</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D53" s="19" t="n">
-        <v>19.6</v>
+        <v>141.4</v>
       </c>
       <c r="E53" s="19" t="n">
-        <v>24.2</v>
+        <v>217.4</v>
       </c>
       <c r="F53" s="19" t="n">
-        <v>211.1</v>
+        <v>502.4</v>
       </c>
       <c r="G53" s="19" t="n">
-        <v>127.2</v>
+        <v>524.6</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>14</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I53" s="19" t="n">
-        <v>93.2</v>
+        <v>225.2</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>28.8</v>
+        <v>108.2</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>518.2</v>
+        <v>1806.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>PJ-2021-E</t>
+          <t>PJ-2021-D</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>シャドウヴェイル</t>
+          <t>蒼穹のレガリア HD Edition(前倒し)</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D54" s="19" t="n">
-        <v>251</v>
+        <v>19.6</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>373</v>
+        <v>24.2</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>795.5</v>
+        <v>211.1</v>
       </c>
       <c r="G54" s="19" t="n">
-        <v>930.9</v>
+        <v>127.2</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>147.4</v>
+        <v>14</v>
       </c>
       <c r="I54" s="19" t="n">
-        <v>346.7</v>
+        <v>93.2</v>
       </c>
       <c r="J54" s="19" t="n">
-        <v>168.9</v>
+        <v>28.8</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>3013.4</v>
+        <v>518.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PJ-2022-F</t>
+          <t>PJ-2021-E</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>ネオンハーツ Season2</t>
+          <t>シャドウヴェイル</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D55" s="19" t="n">
-        <v>51.8</v>
+        <v>251</v>
       </c>
       <c r="E55" s="19" t="n">
-        <v>129.1</v>
+        <v>373</v>
       </c>
       <c r="F55" s="19" t="n">
-        <v>204.3</v>
+        <v>795.5</v>
       </c>
       <c r="G55" s="19" t="n">
-        <v>286.5</v>
+        <v>930.9</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>37.3</v>
+        <v>147.4</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>124.6</v>
+        <v>346.7</v>
       </c>
       <c r="J55" s="19" t="n">
-        <v>48.2</v>
+        <v>168.9</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>881.8</v>
+        <v>3013.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>PJ-2022-G</t>
+          <t>PJ-2022-F</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>ギルドマスターズ(前倒し)</t>
+          <t>ネオンハーツ Season2</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D56" s="19" t="n">
-        <v>123.2</v>
+        <v>51.8</v>
       </c>
       <c r="E56" s="19" t="n">
-        <v>170</v>
+        <v>129.1</v>
       </c>
       <c r="F56" s="19" t="n">
-        <v>392.3</v>
+        <v>204.3</v>
       </c>
       <c r="G56" s="19" t="n">
-        <v>446</v>
+        <v>286.5</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>71.7</v>
+        <v>37.3</v>
       </c>
       <c r="I56" s="19" t="n">
-        <v>171.6</v>
+        <v>124.6</v>
       </c>
       <c r="J56" s="19" t="n">
-        <v>86.40000000000001</v>
+        <v>48.2</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>1461</v>
+        <v>881.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PJ-2023-H</t>
+          <t>PJ-2022-G</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>クロノスギア:蒼き遺産</t>
+          <t>ギルドマスターズ(前倒し)</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D57" s="19" t="n">
-        <v>61.4</v>
+        <v>123.2</v>
       </c>
       <c r="E57" s="19" t="n">
-        <v>155.3</v>
+        <v>170</v>
       </c>
       <c r="F57" s="19" t="n">
-        <v>260.3</v>
+        <v>392.3</v>
       </c>
       <c r="G57" s="19" t="n">
-        <v>371</v>
+        <v>446</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>40.6</v>
+        <v>71.7</v>
       </c>
       <c r="I57" s="19" t="n">
-        <v>150.1</v>
+        <v>171.6</v>
       </c>
       <c r="J57" s="19" t="n">
-        <v>66.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>1104.9</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>PJ-2023-I</t>
+          <t>PJ-2023-H</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>ブレイブフロンティア Remaster</t>
+          <t>クロノスギア:蒼き遺産</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D58" s="19" t="n">
-        <v>29.2</v>
+        <v>61.4</v>
       </c>
       <c r="E58" s="19" t="n">
-        <v>34.4</v>
+        <v>155.3</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>308.5</v>
+        <v>260.3</v>
       </c>
       <c r="G58" s="19" t="n">
-        <v>171.1</v>
+        <v>371</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>20.9</v>
+        <v>40.6</v>
       </c>
       <c r="I58" s="19" t="n">
-        <v>106.1</v>
+        <v>150.1</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>39.5</v>
+        <v>66.3</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>709.7</v>
+        <v>1104.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PJ-2024-J</t>
+          <t>PJ-2023-I</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>オーヴァーロード・サーガ(後半集中)</t>
+          <t>ブレイブフロンティア Remaster</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D59" s="19" t="n">
-        <v>153.8</v>
+        <v>29.2</v>
       </c>
       <c r="E59" s="19" t="n">
-        <v>254</v>
+        <v>34.4</v>
       </c>
       <c r="F59" s="19" t="n">
-        <v>600.1</v>
+        <v>308.5</v>
       </c>
       <c r="G59" s="19" t="n">
-        <v>658.4</v>
+        <v>171.1</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>122.6</v>
+        <v>20.9</v>
       </c>
       <c r="I59" s="19" t="n">
-        <v>234.8</v>
+        <v>106.1</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>138.9</v>
+        <v>39.5</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>2162.6</v>
+        <v>709.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr"/>
-      <c r="C60" s="10" t="n"/>
+          <t>PJ-2024-J</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>オーヴァーロード・サーガ(後半集中)</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>30</v>
+      </c>
       <c r="D60" s="19" t="n">
-        <v>1056.6</v>
+        <v>153.8</v>
       </c>
       <c r="E60" s="19" t="n">
-        <v>1740.3</v>
+        <v>254</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>4009.8</v>
+        <v>600.1</v>
       </c>
       <c r="G60" s="19" t="n">
-        <v>4490.2</v>
+        <v>658.4</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>686.6</v>
+        <v>122.6</v>
       </c>
       <c r="I60" s="19" t="n">
-        <v>1812.3</v>
+        <v>234.8</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>860.1</v>
+        <v>138.9</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>14655.5</v>
+        <v>2162.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="19" t="n">
+        <v>1056.6</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>1740.3</v>
+      </c>
+      <c r="F61" s="19" t="n">
+        <v>4009.8</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>4490.2</v>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>686.6</v>
+      </c>
+      <c r="I61" s="19" t="n">
+        <v>1812.3</v>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v>860.1</v>
+      </c>
+      <c r="K61" s="19" t="n">
+        <v>14655.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
           <t>構成比</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>(全案件の単純合計)</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="17" t="n">
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="17" t="n">
         <v>0.0721</v>
       </c>
-      <c r="E61" s="17" t="n">
+      <c r="E62" s="17" t="n">
         <v>0.1187</v>
       </c>
-      <c r="F61" s="17" t="n">
+      <c r="F62" s="17" t="n">
         <v>0.2736</v>
       </c>
-      <c r="G61" s="17" t="n">
+      <c r="G62" s="17" t="n">
         <v>0.3064</v>
       </c>
-      <c r="H61" s="17" t="n">
+      <c r="H62" s="17" t="n">
         <v>0.0468</v>
       </c>
-      <c r="I61" s="17" t="n">
+      <c r="I62" s="17" t="n">
         <v>0.1237</v>
       </c>
-      <c r="J61" s="17" t="n">
+      <c r="J62" s="17" t="n">
         <v>0.0587</v>
       </c>
-      <c r="K61" s="17" t="n">
+      <c r="K62" s="17" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>■ マイルストーン位置分布(学習値)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>マイルストーン名</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>平均位置</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>標準偏差</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>背骨</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="B65" s="22" t="n">
-        <v>0.2277301327110109</v>
-      </c>
-      <c r="C65" s="22" t="n">
-        <v>0.03189012393515308</v>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>α版</t>
+          <t>プロトタイプ</t>
         </is>
       </c>
       <c r="B66" s="22" t="n">
-        <v>0.4968946897102826</v>
+        <v>0.2277301327110109</v>
       </c>
       <c r="C66" s="22" t="n">
-        <v>0.05787603873596738</v>
+        <v>0.03189012393515308</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>β版</t>
+          <t>α版</t>
         </is>
       </c>
       <c r="B67" s="22" t="n">
-        <v>0.7378800534841294</v>
+        <v>0.4968946897102826</v>
       </c>
       <c r="C67" s="22" t="n">
-        <v>0.05000354072467814</v>
+        <v>0.05787603873596738</v>
       </c>
       <c r="D67" s="10" t="n">
         <v>10</v>
@@ -78849,14 +78875,14 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>マスターアップ</t>
+          <t>β版</t>
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>0.9135394862767734</v>
+        <v>0.7378800534841294</v>
       </c>
       <c r="C68" s="22" t="n">
-        <v>0.01808788952320223</v>
+        <v>0.05000354072467814</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>10</v>
@@ -78867,58 +78893,66 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>マスターアップ</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="n">
+        <v>0.9135394862767734</v>
+      </c>
+      <c r="C69" s="22" t="n">
+        <v>0.01808788952320223</v>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>■ 行程グループ別 工数比率(学習値)</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>件数 = そのグループの形状カーブの学習に参加した案件数。そのグループの業務が無い案件は形の平均に参加しないため、件数が少ないカーブは参考値として扱うこと。比率のほうは業務が無い案件も0として平均に含めている。</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>行程グループ</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>比率</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>企画・プリプロ</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="n">
-        <v>0.06524885174932314</v>
-      </c>
-      <c r="C73" s="11" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>ゲームデザイン・シナリオ</t>
+          <t>企画・プリプロ</t>
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>0.1122043113713705</v>
+        <v>0.06524885174932314</v>
       </c>
       <c r="C74" s="11" t="n">
         <v>10</v>
@@ -78927,11 +78961,11 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>プログラム</t>
+          <t>ゲームデザイン・シナリオ</t>
         </is>
       </c>
       <c r="B75" s="13" t="n">
-        <v>0.2879091969215787</v>
+        <v>0.1122043113713705</v>
       </c>
       <c r="C75" s="11" t="n">
         <v>10</v>
@@ -78940,11 +78974,11 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>アート</t>
+          <t>プログラム</t>
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>0.3005002389104883</v>
+        <v>0.2879091969215787</v>
       </c>
       <c r="C76" s="11" t="n">
         <v>10</v>
@@ -78953,11 +78987,11 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>サウンド</t>
+          <t>アート</t>
         </is>
       </c>
       <c r="B77" s="13" t="n">
-        <v>0.04298558319794448</v>
+        <v>0.3005002389104883</v>
       </c>
       <c r="C77" s="11" t="n">
         <v>10</v>
@@ -78966,11 +79000,11 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>QA・デバッグ</t>
+          <t>サウンド</t>
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>0.1327188838365589</v>
+        <v>0.04298558319794448</v>
       </c>
       <c r="C78" s="11" t="n">
         <v>10</v>
@@ -78979,32 +79013,45 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PM・運営</t>
+          <t>QA・デバッグ</t>
         </is>
       </c>
       <c r="B79" s="13" t="n">
-        <v>0.05843293401273604</v>
+        <v>0.1327188838365589</v>
       </c>
       <c r="C79" s="11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>PM・運営</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="n">
+        <v>0.05843293401273604</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>■ 警告</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="26" t="inlineStr">
-        <is>
-          <t>⚠ マイルストーン「プロトタイプ」はカバー率 5/10 が閾値 60% 未満のため位置合わせには使っていない。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>⚠ マイルストーン「プロトタイプ」はカバー率 5/10 が閾値 60% 未満のため位置合わせには使っていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>⚠ PJ-2021-E は完了案件として学習データに入っているため、段階予測では自分自身を学習から外した 9 件で学習し直している(自分の実績で学習したカーブで自分を予測すると評価にならない)。</t>
         </is>
